--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T10:55:45+00:00</t>
+    <t>2023-04-05T15:18:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T15:18:36+00:00</t>
+    <t>2023-04-05T15:41:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T15:41:27+00:00</t>
+    <t>2023-04-05T15:52:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T15:52:08+00:00</t>
+    <t>2023-04-05T15:53:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T15:53:16+00:00</t>
+    <t>2023-04-05T15:55:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T15:55:13+00:00</t>
+    <t>2023-04-05T16:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3376" uniqueCount="473">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2242" uniqueCount="398">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T16:00:25+00:00</t>
+    <t>2023-04-05T16:20:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -780,162 +780,6 @@
     <t>FiveWs.class</t>
   </si>
   <si>
-    <t>HealthcareService.category.id</t>
-  </si>
-  <si>
-    <t>HealthcareService.category.extension</t>
-  </si>
-  <si>
-    <t>HealthcareService.category.coding</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>HealthcareService.category.coding.id</t>
-  </si>
-  <si>
-    <t>HealthcareService.category.coding.extension</t>
-  </si>
-  <si>
-    <t>HealthcareService.category.coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R275-ModaliteActivite/FHIR/TRE-R275-ModaliteActivite</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>HealthcareService.category.coding.version</t>
-  </si>
-  <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>HealthcareService.category.coding.code</t>
-  </si>
-  <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>HealthcareService.category.coding.display</t>
-  </si>
-  <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>HealthcareService.category.coding.userSelected</t>
-  </si>
-  <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
-    <t>HealthcareService.category.text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
     <t>HealthcareService.type</t>
   </si>
   <si>
@@ -961,42 +805,6 @@
     <t>.actrelationship[typeCode=COMP.act[classCode=ACT][moodCode=DEF].code</t>
   </si>
   <si>
-    <t>HealthcareService.type.id</t>
-  </si>
-  <si>
-    <t>HealthcareService.type.extension</t>
-  </si>
-  <si>
-    <t>HealthcareService.type.coding</t>
-  </si>
-  <si>
-    <t>HealthcareService.type.coding.id</t>
-  </si>
-  <si>
-    <t>HealthcareService.type.coding.extension</t>
-  </si>
-  <si>
-    <t>HealthcareService.type.coding.system</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R274-ActiviteSanitaireRegulee/FHIR/TRE-R274-ActiviteSanitaireRegulee</t>
-  </si>
-  <si>
-    <t>HealthcareService.type.coding.version</t>
-  </si>
-  <si>
-    <t>HealthcareService.type.coding.code</t>
-  </si>
-  <si>
-    <t>HealthcareService.type.coding.display</t>
-  </si>
-  <si>
-    <t>HealthcareService.type.coding.userSelected</t>
-  </si>
-  <si>
-    <t>HealthcareService.type.text</t>
-  </si>
-  <si>
     <t>HealthcareService.specialty</t>
   </si>
   <si>
@@ -1043,6 +851,9 @@
     <t>Further description of the service as it would be presented to a consumer while searching.</t>
   </si>
   <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
+  </si>
+  <si>
     <t>.name</t>
   </si>
   <si>
@@ -1259,42 +1070,6 @@
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J134-FormeActivite-RASS/FHIR/JDV-J134-FormeActivite-RASS</t>
-  </si>
-  <si>
-    <t>HealthcareService.characteristic.id</t>
-  </si>
-  <si>
-    <t>HealthcareService.characteristic.extension</t>
-  </si>
-  <si>
-    <t>HealthcareService.characteristic.coding</t>
-  </si>
-  <si>
-    <t>HealthcareService.characteristic.coding.id</t>
-  </si>
-  <si>
-    <t>HealthcareService.characteristic.coding.extension</t>
-  </si>
-  <si>
-    <t>HealthcareService.characteristic.coding.system</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R276-FormeActivite/FHIR/TRE-R276-FormeActivite</t>
-  </si>
-  <si>
-    <t>HealthcareService.characteristic.coding.version</t>
-  </si>
-  <si>
-    <t>HealthcareService.characteristic.coding.code</t>
-  </si>
-  <si>
-    <t>HealthcareService.characteristic.coding.display</t>
-  </si>
-  <si>
-    <t>HealthcareService.characteristic.coding.userSelected</t>
-  </si>
-  <si>
-    <t>HealthcareService.characteristic.text</t>
   </si>
   <si>
     <t>HealthcareService.communication</t>
@@ -1773,11 +1548,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL98"/>
+  <dimension ref="A1:AL65"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="56.546875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="50.15625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="49.1328125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="29.5703125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
@@ -4850,14 +4625,14 @@
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>73</v>
+        <v>245</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>73</v>
@@ -4866,18 +4641,20 @@
         <v>73</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>97</v>
+        <v>235</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>98</v>
+        <v>246</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>247</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>248</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>73</v>
@@ -4902,13 +4679,13 @@
         <v>73</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>73</v>
+        <v>239</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>73</v>
+        <v>249</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>73</v>
+        <v>250</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>73</v>
@@ -4926,22 +4703,22 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>100</v>
+        <v>244</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>101</v>
+        <v>251</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>73</v>
@@ -4949,21 +4726,21 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>73</v>
@@ -4972,19 +4749,19 @@
         <v>73</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>104</v>
+        <v>235</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>105</v>
+        <v>253</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>106</v>
+        <v>254</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>107</v>
+        <v>248</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5010,31 +4787,31 @@
         <v>73</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>73</v>
+        <v>164</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>73</v>
+        <v>255</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>73</v>
+        <v>256</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>109</v>
+        <v>73</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>111</v>
+        <v>252</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
@@ -5046,10 +4823,10 @@
         <v>93</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>95</v>
+        <v>251</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>73</v>
@@ -5057,10 +4834,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5071,7 +4848,7 @@
         <v>74</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>73</v>
@@ -5083,20 +4860,18 @@
         <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>137</v>
+        <v>258</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>250</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>73</v>
       </c>
@@ -5144,7 +4919,7 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
@@ -5156,21 +4931,21 @@
         <v>93</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>94</v>
+        <v>231</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>73</v>
+        <v>263</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5181,7 +4956,7 @@
         <v>74</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>73</v>
@@ -5190,18 +4965,20 @@
         <v>73</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
         <v>97</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>98</v>
+        <v>265</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>266</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>73</v>
@@ -5250,7 +5027,7 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>100</v>
+        <v>264</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>74</v>
@@ -5259,13 +5036,13 @@
         <v>81</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>101</v>
+        <v>268</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>73</v>
@@ -5273,21 +5050,21 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>254</v>
+        <v>269</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>254</v>
+        <v>269</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>73</v>
@@ -5296,19 +5073,19 @@
         <v>73</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>105</v>
+        <v>270</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>106</v>
+        <v>271</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>107</v>
+        <v>272</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5346,34 +5123,34 @@
         <v>73</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>109</v>
+        <v>73</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>111</v>
+        <v>269</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>95</v>
+        <v>273</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>73</v>
@@ -5381,10 +5158,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>255</v>
+        <v>274</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>255</v>
+        <v>274</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5395,7 +5172,7 @@
         <v>74</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>73</v>
@@ -5404,29 +5181,27 @@
         <v>73</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>125</v>
+        <v>275</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>256</v>
+        <v>276</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>257</v>
+        <v>277</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>259</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>73</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>260</v>
+        <v>73</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>73</v>
@@ -5468,7 +5243,7 @@
         <v>73</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>74</v>
@@ -5483,7 +5258,7 @@
         <v>94</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>73</v>
@@ -5491,10 +5266,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>263</v>
+        <v>280</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>263</v>
+        <v>280</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5505,7 +5280,7 @@
         <v>74</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>73</v>
@@ -5517,16 +5292,16 @@
         <v>82</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>97</v>
+        <v>281</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>264</v>
+        <v>282</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>265</v>
+        <v>283</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>266</v>
+        <v>284</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5576,7 +5351,7 @@
         <v>73</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>267</v>
+        <v>280</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>74</v>
@@ -5588,10 +5363,10 @@
         <v>93</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>94</v>
+        <v>285</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>268</v>
+        <v>286</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>73</v>
@@ -5599,10 +5374,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>269</v>
+        <v>287</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>269</v>
+        <v>287</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5613,7 +5388,7 @@
         <v>74</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>73</v>
@@ -5622,23 +5397,21 @@
         <v>73</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>160</v>
+        <v>288</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>270</v>
+        <v>289</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>271</v>
+        <v>290</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>273</v>
-      </c>
+        <v>291</v>
+      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>73</v>
       </c>
@@ -5686,22 +5459,22 @@
         <v>73</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>274</v>
+        <v>287</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>94</v>
+        <v>292</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>275</v>
+        <v>293</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>73</v>
@@ -5709,10 +5482,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5723,7 +5496,7 @@
         <v>74</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>73</v>
@@ -5732,23 +5505,21 @@
         <v>73</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>97</v>
+        <v>258</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>277</v>
+        <v>295</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>278</v>
+        <v>296</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>279</v>
-      </c>
+        <v>297</v>
+      </c>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>73</v>
       </c>
@@ -5796,22 +5567,22 @@
         <v>73</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>280</v>
+        <v>294</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>94</v>
+        <v>231</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>281</v>
+        <v>298</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>73</v>
@@ -5819,10 +5590,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5833,7 +5604,7 @@
         <v>74</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>73</v>
@@ -5842,23 +5613,21 @@
         <v>73</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>219</v>
+        <v>235</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>283</v>
+        <v>300</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>284</v>
+        <v>301</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>73</v>
       </c>
@@ -5882,13 +5651,13 @@
         <v>73</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>73</v>
+        <v>150</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>73</v>
+        <v>301</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>73</v>
+        <v>303</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>73</v>
@@ -5906,13 +5675,13 @@
         <v>73</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>93</v>
@@ -5921,7 +5690,7 @@
         <v>94</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>288</v>
+        <v>304</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>73</v>
@@ -5929,10 +5698,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5943,7 +5712,7 @@
         <v>74</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>73</v>
@@ -5952,23 +5721,19 @@
         <v>73</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>97</v>
+        <v>306</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>290</v>
+        <v>307</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>293</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>73</v>
       </c>
@@ -6016,13 +5781,13 @@
         <v>73</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>93</v>
@@ -6031,7 +5796,7 @@
         <v>94</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>295</v>
+        <v>101</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>73</v>
@@ -6039,21 +5804,21 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>297</v>
+        <v>73</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>73</v>
@@ -6062,20 +5827,18 @@
         <v>73</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>235</v>
+        <v>97</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>298</v>
+        <v>98</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>300</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>73</v>
@@ -6100,13 +5863,13 @@
         <v>73</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>239</v>
+        <v>73</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>301</v>
+        <v>73</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>302</v>
+        <v>73</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>73</v>
@@ -6124,22 +5887,22 @@
         <v>73</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>296</v>
+        <v>100</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>303</v>
+        <v>101</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>73</v>
@@ -6147,21 +5910,21 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>73</v>
@@ -6173,15 +5936,17 @@
         <v>73</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>106</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>73</v>
@@ -6218,34 +5983,34 @@
         <v>73</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>73</v>
+        <v>109</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>73</v>
+        <v>112</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>73</v>
@@ -6253,14 +6018,14 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>103</v>
+        <v>312</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6273,24 +6038,26 @@
         <v>73</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
         <v>104</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>105</v>
+        <v>313</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>106</v>
+        <v>314</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="O42" s="2"/>
+      <c r="O42" t="s" s="2">
+        <v>210</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>73</v>
       </c>
@@ -6326,19 +6093,19 @@
         <v>73</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>109</v>
+        <v>73</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>111</v>
+        <v>315</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>74</v>
@@ -6361,10 +6128,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6375,7 +6142,7 @@
         <v>74</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>73</v>
@@ -6384,23 +6151,21 @@
         <v>73</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>137</v>
+        <v>235</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>247</v>
+        <v>317</v>
       </c>
       <c r="M43" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="N43" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="N43" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>250</v>
-      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>73</v>
       </c>
@@ -6424,10 +6189,10 @@
         <v>73</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>73</v>
+        <v>150</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>73</v>
+        <v>319</v>
       </c>
       <c r="Z43" t="s" s="2">
         <v>73</v>
@@ -6448,13 +6213,13 @@
         <v>73</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>251</v>
+        <v>316</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>93</v>
@@ -6463,7 +6228,7 @@
         <v>94</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>252</v>
+        <v>304</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>73</v>
@@ -6471,10 +6236,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6497,15 +6262,17 @@
         <v>73</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>97</v>
+        <v>275</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>98</v>
+        <v>321</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>322</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>323</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>73</v>
@@ -6554,7 +6321,7 @@
         <v>73</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>100</v>
+        <v>320</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>74</v>
@@ -6563,13 +6330,13 @@
         <v>81</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>101</v>
+        <v>324</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>73</v>
@@ -6577,21 +6344,21 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>308</v>
+        <v>325</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>308</v>
+        <v>325</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>73</v>
@@ -6603,16 +6370,16 @@
         <v>73</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>104</v>
+        <v>235</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>105</v>
+        <v>326</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>106</v>
+        <v>327</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>107</v>
+        <v>328</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6638,31 +6405,31 @@
         <v>73</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>73</v>
+        <v>150</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>73</v>
+        <v>329</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>73</v>
+        <v>330</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>109</v>
+        <v>73</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>111</v>
+        <v>325</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>74</v>
@@ -6674,10 +6441,10 @@
         <v>93</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>95</v>
+        <v>331</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>73</v>
@@ -6685,10 +6452,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>309</v>
+        <v>332</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>309</v>
+        <v>332</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6699,7 +6466,7 @@
         <v>74</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>73</v>
@@ -6708,29 +6475,27 @@
         <v>73</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>125</v>
+        <v>235</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>256</v>
+        <v>333</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>257</v>
+        <v>334</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>259</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>73</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
-        <v>310</v>
+        <v>73</v>
       </c>
       <c r="S46" t="s" s="2">
         <v>73</v>
@@ -6748,13 +6513,13 @@
         <v>73</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>73</v>
+        <v>239</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>73</v>
+        <v>336</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>73</v>
+        <v>337</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>73</v>
@@ -6772,13 +6537,13 @@
         <v>73</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>261</v>
+        <v>332</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>93</v>
@@ -6787,7 +6552,7 @@
         <v>94</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>262</v>
+        <v>331</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>73</v>
@@ -6795,10 +6560,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>311</v>
+        <v>338</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>311</v>
+        <v>338</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6809,7 +6574,7 @@
         <v>74</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>73</v>
@@ -6818,19 +6583,19 @@
         <v>73</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>97</v>
+        <v>235</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>264</v>
+        <v>339</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>265</v>
+        <v>340</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>266</v>
+        <v>341</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6856,13 +6621,13 @@
         <v>73</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>73</v>
+        <v>164</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>73</v>
+        <v>165</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>73</v>
+        <v>166</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>73</v>
@@ -6880,13 +6645,13 @@
         <v>73</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>267</v>
+        <v>338</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>93</v>
@@ -6895,7 +6660,7 @@
         <v>94</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>268</v>
+        <v>342</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>73</v>
@@ -6903,10 +6668,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>312</v>
+        <v>343</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>312</v>
+        <v>343</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6917,7 +6682,7 @@
         <v>74</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>73</v>
@@ -6926,23 +6691,21 @@
         <v>73</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>160</v>
+        <v>235</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>270</v>
+        <v>344</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>271</v>
+        <v>345</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>273</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>73</v>
       </c>
@@ -6966,13 +6729,13 @@
         <v>73</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>73</v>
+        <v>150</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>73</v>
+        <v>346</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>73</v>
+        <v>347</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>73</v>
@@ -6990,13 +6753,13 @@
         <v>73</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>274</v>
+        <v>343</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>93</v>
@@ -7005,7 +6768,7 @@
         <v>94</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>275</v>
+        <v>331</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>73</v>
@@ -7013,10 +6776,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>313</v>
+        <v>348</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>313</v>
+        <v>348</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7027,7 +6790,7 @@
         <v>74</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>73</v>
@@ -7036,23 +6799,19 @@
         <v>73</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>97</v>
+        <v>219</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>277</v>
+        <v>349</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>279</v>
-      </c>
+        <v>350</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>73</v>
       </c>
@@ -7100,7 +6859,7 @@
         <v>73</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>280</v>
+        <v>348</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>74</v>
@@ -7115,7 +6874,7 @@
         <v>94</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>281</v>
+        <v>331</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>73</v>
@@ -7123,10 +6882,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>314</v>
+        <v>351</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>314</v>
+        <v>351</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7137,7 +6896,7 @@
         <v>74</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>73</v>
@@ -7146,23 +6905,21 @@
         <v>73</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>219</v>
+        <v>306</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>283</v>
+        <v>352</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>284</v>
+        <v>353</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>354</v>
+      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>73</v>
       </c>
@@ -7210,13 +6967,13 @@
         <v>73</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>287</v>
+        <v>351</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>93</v>
@@ -7225,7 +6982,7 @@
         <v>94</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>288</v>
+        <v>355</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>73</v>
@@ -7233,10 +6990,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7256,23 +7013,19 @@
         <v>73</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K51" t="s" s="2">
         <v>97</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>290</v>
+        <v>98</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>293</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>73</v>
       </c>
@@ -7320,7 +7073,7 @@
         <v>73</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>294</v>
+        <v>100</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>74</v>
@@ -7329,13 +7082,13 @@
         <v>81</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>295</v>
+        <v>101</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>73</v>
@@ -7343,21 +7096,21 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>316</v>
+        <v>357</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>316</v>
+        <v>357</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>73</v>
@@ -7366,19 +7119,19 @@
         <v>73</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>235</v>
+        <v>104</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>317</v>
+        <v>105</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>318</v>
+        <v>106</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>300</v>
+        <v>107</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7404,31 +7157,31 @@
         <v>73</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>164</v>
+        <v>73</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>319</v>
+        <v>73</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>320</v>
+        <v>73</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>73</v>
+        <v>109</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>316</v>
+        <v>111</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>74</v>
@@ -7440,10 +7193,10 @@
         <v>93</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>303</v>
+        <v>95</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>73</v>
@@ -7451,44 +7204,46 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>321</v>
+        <v>358</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>321</v>
+        <v>358</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>73</v>
+        <v>312</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="J53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>322</v>
+        <v>104</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="O53" s="2"/>
+        <v>107</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>210</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>73</v>
       </c>
@@ -7536,7 +7291,7 @@
         <v>73</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>74</v>
@@ -7548,21 +7303,21 @@
         <v>93</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>231</v>
+        <v>112</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>326</v>
+        <v>95</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>327</v>
+        <v>73</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>328</v>
+        <v>359</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>328</v>
+        <v>359</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7573,7 +7328,7 @@
         <v>74</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>73</v>
@@ -7582,19 +7337,19 @@
         <v>73</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>97</v>
+        <v>160</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>329</v>
+        <v>360</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>330</v>
+        <v>361</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7620,13 +7375,13 @@
         <v>73</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>73</v>
+        <v>239</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>73</v>
+        <v>362</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>73</v>
+        <v>363</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>73</v>
@@ -7644,13 +7399,13 @@
         <v>73</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>328</v>
+        <v>359</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>93</v>
@@ -7659,7 +7414,7 @@
         <v>94</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>331</v>
+        <v>355</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>73</v>
@@ -7667,10 +7422,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>332</v>
+        <v>364</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>332</v>
+        <v>364</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7681,7 +7436,7 @@
         <v>74</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>73</v>
@@ -7690,20 +7445,18 @@
         <v>73</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>97</v>
+        <v>219</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>333</v>
+        <v>365</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>335</v>
-      </c>
+        <v>366</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>73</v>
@@ -7752,7 +7505,7 @@
         <v>73</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>332</v>
+        <v>364</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>74</v>
@@ -7767,7 +7520,7 @@
         <v>94</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>336</v>
+        <v>355</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>73</v>
@@ -7775,10 +7528,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>337</v>
+        <v>367</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>337</v>
+        <v>367</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7789,7 +7542,7 @@
         <v>74</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>73</v>
@@ -7801,16 +7554,16 @@
         <v>73</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>338</v>
+        <v>368</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>339</v>
+        <v>369</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>340</v>
+        <v>370</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>341</v>
+        <v>371</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -7860,7 +7613,7 @@
         <v>73</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>337</v>
+        <v>367</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>74</v>
@@ -7875,7 +7628,7 @@
         <v>94</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>342</v>
+        <v>355</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>73</v>
@@ -7883,10 +7636,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>343</v>
+        <v>372</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>343</v>
+        <v>372</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7897,7 +7650,7 @@
         <v>74</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>73</v>
@@ -7906,19 +7659,19 @@
         <v>73</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>344</v>
+        <v>368</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>345</v>
+        <v>373</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>346</v>
+        <v>374</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>347</v>
+        <v>371</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -7968,7 +7721,7 @@
         <v>73</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>343</v>
+        <v>372</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>74</v>
@@ -7980,10 +7733,10 @@
         <v>93</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>348</v>
+        <v>94</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>73</v>
@@ -7991,10 +7744,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>350</v>
+        <v>375</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>350</v>
+        <v>375</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8017,17 +7770,15 @@
         <v>73</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>351</v>
+        <v>306</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>352</v>
+        <v>376</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>354</v>
-      </c>
+        <v>377</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>73</v>
@@ -8076,7 +7827,7 @@
         <v>73</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>350</v>
+        <v>375</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>74</v>
@@ -8088,10 +7839,10 @@
         <v>93</v>
       </c>
       <c r="AJ58" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AK58" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="AK58" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>73</v>
@@ -8099,10 +7850,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>357</v>
+        <v>378</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>357</v>
+        <v>378</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8113,7 +7864,7 @@
         <v>74</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>73</v>
@@ -8125,17 +7876,15 @@
         <v>73</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>322</v>
+        <v>97</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>358</v>
+        <v>98</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>360</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>73</v>
@@ -8184,22 +7933,22 @@
         <v>73</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>357</v>
+        <v>100</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>231</v>
+        <v>73</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>361</v>
+        <v>101</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>73</v>
@@ -8207,21 +7956,21 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>362</v>
+        <v>379</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>362</v>
+        <v>379</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>73</v>
@@ -8233,16 +7982,16 @@
         <v>73</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>235</v>
+        <v>104</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>363</v>
+        <v>105</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>364</v>
+        <v>106</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>365</v>
+        <v>107</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8268,31 +8017,31 @@
         <v>73</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>150</v>
+        <v>73</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>364</v>
+        <v>73</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>366</v>
+        <v>73</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>73</v>
+        <v>109</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>362</v>
+        <v>111</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>74</v>
@@ -8304,10 +8053,10 @@
         <v>93</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>367</v>
+        <v>95</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>73</v>
@@ -8315,42 +8064,46 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>73</v>
+        <v>312</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>369</v>
+        <v>104</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>370</v>
+        <v>313</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
+        <v>314</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>210</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>73</v>
       </c>
@@ -8398,7 +8151,7 @@
         <v>73</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>368</v>
+        <v>315</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>74</v>
@@ -8410,10 +8163,10 @@
         <v>93</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>73</v>
@@ -8421,10 +8174,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8432,7 +8185,7 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G62" t="s" s="2">
         <v>81</v>
@@ -8450,12 +8203,14 @@
         <v>97</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>98</v>
+        <v>382</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N62" s="2"/>
+        <v>383</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>73</v>
@@ -8504,19 +8259,19 @@
         <v>73</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>100</v>
+        <v>381</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AH62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>101</v>
@@ -8527,21 +8282,21 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>73</v>
@@ -8553,16 +8308,16 @@
         <v>73</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>104</v>
+        <v>385</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>105</v>
+        <v>386</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>106</v>
+        <v>387</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>107</v>
+        <v>388</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -8600,34 +8355,34 @@
         <v>73</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>109</v>
+        <v>73</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>111</v>
+        <v>384</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>112</v>
+        <v>389</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>95</v>
+        <v>355</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>73</v>
@@ -8635,46 +8390,44 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>374</v>
+        <v>390</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>374</v>
+        <v>390</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>375</v>
+        <v>73</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>376</v>
+        <v>391</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>377</v>
+        <v>392</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>210</v>
-      </c>
+        <v>267</v>
+      </c>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>73</v>
       </c>
@@ -8722,22 +8475,22 @@
         <v>73</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>95</v>
+        <v>355</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>73</v>
@@ -8745,10 +8498,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8759,7 +8512,7 @@
         <v>74</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>73</v>
@@ -8771,16 +8524,16 @@
         <v>73</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>235</v>
+        <v>394</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>380</v>
+        <v>395</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>381</v>
+        <v>396</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>300</v>
+        <v>261</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -8806,10 +8559,10 @@
         <v>73</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>150</v>
+        <v>73</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>382</v>
+        <v>73</v>
       </c>
       <c r="Z65" t="s" s="2">
         <v>73</v>
@@ -8830,3590 +8583,24 @@
         <v>73</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>94</v>
+        <v>231</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>367</v>
+        <v>397</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="C66" s="2"/>
-      <c r="D66" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E66" s="2"/>
-      <c r="F66" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H66" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I66" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J66" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K66" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="L66" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="O66" s="2"/>
-      <c r="P66" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q66" s="2"/>
-      <c r="R66" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S66" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T66" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U66" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V66" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W66" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X66" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z66" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA66" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF66" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="AG66" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI66" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ66" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK66" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="AL66" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="C67" s="2"/>
-      <c r="D67" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E67" s="2"/>
-      <c r="F67" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G67" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H67" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I67" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J67" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K67" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="L67" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="O67" s="2"/>
-      <c r="P67" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q67" s="2"/>
-      <c r="R67" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S67" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T67" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U67" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V67" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W67" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X67" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="Y67" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="Z67" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="AA67" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="AG67" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH67" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI67" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ67" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK67" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="AL67" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="C68" s="2"/>
-      <c r="D68" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E68" s="2"/>
-      <c r="F68" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G68" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H68" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I68" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J68" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K68" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="L68" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="O68" s="2"/>
-      <c r="P68" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q68" s="2"/>
-      <c r="R68" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S68" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T68" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U68" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V68" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W68" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X68" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="Y68" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="Z68" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="AG68" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH68" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI68" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ68" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK68" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="AL68" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="C69" s="2"/>
-      <c r="D69" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E69" s="2"/>
-      <c r="F69" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H69" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I69" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J69" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K69" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="L69" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" s="2"/>
-      <c r="P69" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q69" s="2"/>
-      <c r="R69" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S69" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T69" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U69" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V69" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W69" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X69" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y69" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z69" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AG69" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI69" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ69" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AK69" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AL69" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="C70" s="2"/>
-      <c r="D70" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="E70" s="2"/>
-      <c r="F70" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G70" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H70" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I70" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J70" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K70" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L70" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="O70" s="2"/>
-      <c r="P70" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q70" s="2"/>
-      <c r="R70" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S70" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T70" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U70" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V70" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W70" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X70" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y70" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z70" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA70" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB70" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AD70" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="AG70" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH70" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI70" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ70" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="AK70" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AL70" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="C71" s="2"/>
-      <c r="D71" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E71" s="2"/>
-      <c r="F71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G71" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H71" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I71" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K71" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="L71" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="P71" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q71" s="2"/>
-      <c r="R71" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S71" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T71" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U71" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V71" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W71" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X71" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y71" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z71" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="AG71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH71" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI71" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ71" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK71" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="AL71" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="C72" s="2"/>
-      <c r="D72" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E72" s="2"/>
-      <c r="F72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H72" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I72" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J72" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K72" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="L72" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N72" s="2"/>
-      <c r="O72" s="2"/>
-      <c r="P72" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q72" s="2"/>
-      <c r="R72" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S72" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T72" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U72" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V72" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W72" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X72" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z72" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AG72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI72" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ72" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AK72" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AL72" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="C73" s="2"/>
-      <c r="D73" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="E73" s="2"/>
-      <c r="F73" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G73" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H73" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I73" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J73" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K73" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L73" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="O73" s="2"/>
-      <c r="P73" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q73" s="2"/>
-      <c r="R73" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S73" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T73" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U73" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V73" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W73" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X73" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z73" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA73" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB73" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="AG73" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH73" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI73" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ73" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="AK73" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="C74" s="2"/>
-      <c r="D74" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E74" s="2"/>
-      <c r="F74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H74" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I74" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K74" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="L74" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="P74" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q74" s="2"/>
-      <c r="R74" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="S74" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T74" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U74" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V74" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W74" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X74" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y74" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z74" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="AG74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI74" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ74" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK74" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="B75" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="C75" s="2"/>
-      <c r="D75" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E75" s="2"/>
-      <c r="F75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H75" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I75" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K75" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="L75" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="O75" s="2"/>
-      <c r="P75" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q75" s="2"/>
-      <c r="R75" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S75" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T75" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U75" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V75" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W75" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X75" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y75" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z75" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA75" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB75" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD75" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE75" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF75" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="AG75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI75" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ75" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK75" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="AL75" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="B76" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="C76" s="2"/>
-      <c r="D76" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E76" s="2"/>
-      <c r="F76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H76" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I76" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K76" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="L76" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="P76" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q76" s="2"/>
-      <c r="R76" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S76" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T76" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U76" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V76" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W76" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X76" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y76" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z76" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="AG76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI76" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ76" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK76" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="AL76" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="C77" s="2"/>
-      <c r="D77" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E77" s="2"/>
-      <c r="F77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H77" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I77" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K77" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="L77" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="P77" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q77" s="2"/>
-      <c r="R77" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S77" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T77" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U77" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V77" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W77" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X77" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y77" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z77" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="AG77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI77" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ77" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK77" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="AL77" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="B78" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="C78" s="2"/>
-      <c r="D78" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E78" s="2"/>
-      <c r="F78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H78" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I78" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K78" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="L78" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="P78" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q78" s="2"/>
-      <c r="R78" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S78" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T78" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U78" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V78" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W78" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X78" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z78" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA78" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB78" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD78" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE78" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF78" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="AG78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI78" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ78" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK78" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="AL78" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="C79" s="2"/>
-      <c r="D79" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E79" s="2"/>
-      <c r="F79" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H79" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I79" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K79" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="L79" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="P79" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q79" s="2"/>
-      <c r="R79" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S79" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T79" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U79" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V79" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W79" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X79" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y79" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z79" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA79" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB79" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC79" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD79" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE79" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF79" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="AG79" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI79" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ79" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK79" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="AL79" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="B80" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="C80" s="2"/>
-      <c r="D80" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E80" s="2"/>
-      <c r="F80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H80" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I80" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J80" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K80" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="L80" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="O80" s="2"/>
-      <c r="P80" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q80" s="2"/>
-      <c r="R80" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S80" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T80" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U80" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V80" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W80" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X80" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="Y80" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="Z80" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="AA80" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB80" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD80" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="AG80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI80" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ80" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK80" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="AL80" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="B81" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="C81" s="2"/>
-      <c r="D81" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E81" s="2"/>
-      <c r="F81" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G81" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H81" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I81" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J81" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K81" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="L81" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="O81" s="2"/>
-      <c r="P81" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q81" s="2"/>
-      <c r="R81" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S81" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T81" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U81" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V81" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W81" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X81" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="Y81" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="Z81" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="AA81" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB81" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC81" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD81" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE81" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF81" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="AG81" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI81" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ81" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK81" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="AL81" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="B82" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="C82" s="2"/>
-      <c r="D82" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E82" s="2"/>
-      <c r="F82" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G82" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H82" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I82" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J82" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K82" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="L82" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="N82" s="2"/>
-      <c r="O82" s="2"/>
-      <c r="P82" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q82" s="2"/>
-      <c r="R82" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S82" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T82" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U82" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V82" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W82" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X82" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y82" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z82" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA82" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB82" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="AG82" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI82" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ82" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK82" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="AL82" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="B83" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="C83" s="2"/>
-      <c r="D83" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E83" s="2"/>
-      <c r="F83" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G83" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H83" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I83" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J83" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K83" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="L83" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="O83" s="2"/>
-      <c r="P83" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q83" s="2"/>
-      <c r="R83" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S83" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T83" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U83" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V83" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W83" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X83" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y83" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z83" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA83" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB83" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD83" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE83" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF83" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="AG83" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI83" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ83" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK83" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="AL83" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="B84" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="C84" s="2"/>
-      <c r="D84" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E84" s="2"/>
-      <c r="F84" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H84" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I84" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J84" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K84" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="L84" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N84" s="2"/>
-      <c r="O84" s="2"/>
-      <c r="P84" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q84" s="2"/>
-      <c r="R84" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S84" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T84" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U84" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V84" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W84" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X84" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y84" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z84" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA84" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB84" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD84" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE84" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF84" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AG84" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI84" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ84" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AK84" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AL84" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="B85" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="C85" s="2"/>
-      <c r="D85" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="E85" s="2"/>
-      <c r="F85" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H85" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I85" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J85" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K85" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L85" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="O85" s="2"/>
-      <c r="P85" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q85" s="2"/>
-      <c r="R85" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S85" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T85" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U85" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V85" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W85" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X85" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y85" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z85" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA85" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB85" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AC85" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AD85" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE85" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="AF85" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="AG85" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI85" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ85" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="AK85" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AL85" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="B86" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="C86" s="2"/>
-      <c r="D86" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="E86" s="2"/>
-      <c r="F86" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G86" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H86" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K86" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L86" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="P86" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q86" s="2"/>
-      <c r="R86" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S86" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T86" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U86" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V86" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W86" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X86" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y86" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z86" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA86" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB86" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC86" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD86" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE86" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF86" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="AG86" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH86" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI86" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ86" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="AK86" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AL86" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="B87" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="C87" s="2"/>
-      <c r="D87" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E87" s="2"/>
-      <c r="F87" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H87" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I87" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J87" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K87" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="L87" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="O87" s="2"/>
-      <c r="P87" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q87" s="2"/>
-      <c r="R87" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S87" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T87" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U87" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V87" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W87" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X87" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="Y87" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="Z87" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="AA87" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB87" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC87" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD87" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE87" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF87" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="AG87" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI87" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ87" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK87" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="AL87" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="B88" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="C88" s="2"/>
-      <c r="D88" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E88" s="2"/>
-      <c r="F88" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H88" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I88" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J88" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K88" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="L88" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="N88" s="2"/>
-      <c r="O88" s="2"/>
-      <c r="P88" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q88" s="2"/>
-      <c r="R88" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S88" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T88" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U88" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V88" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W88" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X88" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y88" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z88" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA88" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB88" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC88" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD88" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE88" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF88" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="AG88" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI88" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ88" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK88" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="AL88" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="B89" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="C89" s="2"/>
-      <c r="D89" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E89" s="2"/>
-      <c r="F89" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H89" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I89" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J89" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K89" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="L89" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="O89" s="2"/>
-      <c r="P89" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q89" s="2"/>
-      <c r="R89" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S89" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T89" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U89" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V89" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W89" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X89" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y89" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z89" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA89" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB89" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC89" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD89" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE89" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF89" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="AG89" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI89" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ89" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK89" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="AL89" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="B90" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="C90" s="2"/>
-      <c r="D90" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E90" s="2"/>
-      <c r="F90" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H90" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I90" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J90" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K90" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="L90" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="O90" s="2"/>
-      <c r="P90" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q90" s="2"/>
-      <c r="R90" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S90" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T90" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U90" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V90" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W90" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X90" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y90" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z90" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA90" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB90" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC90" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD90" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE90" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF90" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="AG90" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI90" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ90" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK90" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="AL90" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="B91" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="C91" s="2"/>
-      <c r="D91" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E91" s="2"/>
-      <c r="F91" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G91" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H91" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I91" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J91" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K91" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="L91" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="M91" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="N91" s="2"/>
-      <c r="O91" s="2"/>
-      <c r="P91" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q91" s="2"/>
-      <c r="R91" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S91" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T91" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U91" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V91" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W91" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X91" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y91" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z91" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA91" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB91" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC91" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD91" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE91" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF91" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="AG91" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI91" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ91" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK91" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="AL91" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="B92" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="C92" s="2"/>
-      <c r="D92" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E92" s="2"/>
-      <c r="F92" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H92" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I92" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J92" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K92" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="L92" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="M92" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N92" s="2"/>
-      <c r="O92" s="2"/>
-      <c r="P92" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q92" s="2"/>
-      <c r="R92" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S92" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T92" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U92" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V92" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W92" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X92" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y92" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z92" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA92" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB92" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC92" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD92" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE92" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF92" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AG92" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI92" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ92" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AK92" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AL92" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="B93" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="C93" s="2"/>
-      <c r="D93" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="E93" s="2"/>
-      <c r="F93" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H93" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I93" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J93" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K93" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L93" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="O93" s="2"/>
-      <c r="P93" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q93" s="2"/>
-      <c r="R93" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S93" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T93" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U93" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V93" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W93" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X93" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y93" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z93" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA93" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB93" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AC93" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AD93" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE93" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="AF93" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="AG93" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI93" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ93" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="AK93" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AL93" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="B94" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="C94" s="2"/>
-      <c r="D94" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="E94" s="2"/>
-      <c r="F94" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H94" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K94" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L94" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="P94" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q94" s="2"/>
-      <c r="R94" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S94" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T94" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U94" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V94" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W94" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X94" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y94" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z94" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA94" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB94" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC94" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD94" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE94" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF94" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="AG94" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI94" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ94" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="AK94" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AL94" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="B95" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="C95" s="2"/>
-      <c r="D95" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E95" s="2"/>
-      <c r="F95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H95" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I95" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J95" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K95" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="L95" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="O95" s="2"/>
-      <c r="P95" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q95" s="2"/>
-      <c r="R95" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S95" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T95" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U95" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V95" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W95" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X95" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y95" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z95" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA95" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB95" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC95" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD95" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE95" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF95" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="AG95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI95" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ95" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK95" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AL95" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="B96" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="C96" s="2"/>
-      <c r="D96" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E96" s="2"/>
-      <c r="F96" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H96" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I96" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J96" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K96" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="L96" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="O96" s="2"/>
-      <c r="P96" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q96" s="2"/>
-      <c r="R96" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S96" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T96" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U96" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V96" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W96" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X96" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y96" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z96" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA96" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB96" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC96" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD96" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE96" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF96" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="AG96" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI96" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ96" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="AK96" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="AL96" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="B97" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="C97" s="2"/>
-      <c r="D97" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E97" s="2"/>
-      <c r="F97" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G97" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H97" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I97" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J97" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K97" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="L97" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="O97" s="2"/>
-      <c r="P97" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q97" s="2"/>
-      <c r="R97" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S97" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T97" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U97" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V97" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W97" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X97" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y97" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z97" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA97" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB97" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC97" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD97" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE97" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF97" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="AG97" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI97" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ97" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK97" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="AL97" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="B98" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="C98" s="2"/>
-      <c r="D98" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E98" s="2"/>
-      <c r="F98" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G98" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H98" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I98" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J98" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K98" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="L98" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="O98" s="2"/>
-      <c r="P98" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q98" s="2"/>
-      <c r="R98" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S98" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T98" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U98" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V98" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W98" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X98" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y98" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z98" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA98" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB98" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC98" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD98" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE98" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF98" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="AG98" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI98" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ98" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="AK98" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="AL98" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T16:20:25+00:00</t>
+    <t>2023-04-05T16:21:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T16:21:30+00:00</t>
+    <t>2023-04-05T16:24:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T16:24:37+00:00</t>
+    <t>2023-04-05T17:39:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T17:39:15+00:00</t>
+    <t>2023-04-07T12:42:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-07T12:42:40+00:00</t>
+    <t>2023-04-12T10:00:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-12T10:00:48+00:00</t>
+    <t>2023-04-12T10:05:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -9,11 +9,14 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$57</definedName>
+  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2242" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1971" uniqueCount="357">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-12T10:05:52+00:00</t>
+    <t>2023-04-12T10:08:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -308,543 +311,395 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>HealthcareService.meta.id</t>
+    <t>HealthcareService.implicitRules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uri
+</t>
+  </si>
+  <si>
+    <t>A set of rules under which this content was created</t>
+  </si>
+  <si>
+    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+  </si>
+  <si>
+    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+  </si>
+  <si>
+    <t>Resource.implicitRules</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>HealthcareService.language</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code
+</t>
+  </si>
+  <si>
+    <t>Language of the resource content</t>
+  </si>
+  <si>
+    <t>The base language in which the resource is written.</t>
+  </si>
+  <si>
+    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
+  </si>
+  <si>
+    <t>preferred</t>
+  </si>
+  <si>
+    <t>A human language.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
+  </si>
+  <si>
+    <t>Resource.language</t>
+  </si>
+  <si>
+    <t>HealthcareService.text</t>
+  </si>
+  <si>
+    <t>narrative
+htmlxhtmldisplay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narrative
+</t>
+  </si>
+  <si>
+    <t>Text summary of the resource, for human interpretation</t>
+  </si>
+  <si>
+    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
+  </si>
+  <si>
+    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+  </si>
+  <si>
+    <t>DomainResource.text</t>
+  </si>
+  <si>
+    <t>Act.text?</t>
+  </si>
+  <si>
+    <t>HealthcareService.contained</t>
+  </si>
+  <si>
+    <t>inline resources
+anonymous resourcescontained resources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resource
+</t>
+  </si>
+  <si>
+    <t>Contained, inline Resources</t>
+  </si>
+  <si>
+    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
+  </si>
+  <si>
+    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+  </si>
+  <si>
+    <t>DomainResource.contained</t>
+  </si>
+  <si>
+    <t>HealthcareService.extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>HealthcareService.extension:activityType</t>
+  </si>
+  <si>
+    <t>activityType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/HealthcareService-activityType}
+</t>
+  </si>
+  <si>
+    <t>Optional Extensions Element</t>
+  </si>
+  <si>
+    <t>Optional Extension Element - found in all resources.</t>
+  </si>
+  <si>
+    <t>HealthcareService.extension:authorizationDate</t>
+  </si>
+  <si>
+    <t>authorizationDate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/HealthcareService-authorizationDate}
+</t>
+  </si>
+  <si>
+    <t>HealthcareService.extension:authorizationNumberARHGOS</t>
+  </si>
+  <si>
+    <t>authorizationNumberARHGOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/HealthcareService-authorizationNumberARHGOS}
+</t>
+  </si>
+  <si>
+    <t>HealthcareService.extension:implementationPeriod</t>
+  </si>
+  <si>
+    <t>implementationPeriod</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/HealthcareService-implementationPeriod}
+</t>
+  </si>
+  <si>
+    <t>HealthcareService.extension:deleteAutorisationImplantation</t>
+  </si>
+  <si>
+    <t>deleteAutorisationImplantation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/HealthcareService-deleteAutorisationImplantation}
+</t>
+  </si>
+  <si>
+    <t>HealthcareService.extension:dateUpdateActivity</t>
+  </si>
+  <si>
+    <t>dateUpdateActivity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/HealthcareService-dateUpdateActivity}
+</t>
+  </si>
+  <si>
+    <t>HealthcareService.modifierExtension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+  </si>
+  <si>
+    <t>DomainResource.modifierExtension</t>
+  </si>
+  <si>
+    <t>HealthcareService.identifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier
+</t>
+  </si>
+  <si>
+    <t>Numéro autorisation ARGHOS</t>
+  </si>
+  <si>
+    <t>External identifiers for this item.</t>
+  </si>
+  <si>
+    <t>.id</t>
+  </si>
+  <si>
+    <t>FiveWs.identifier</t>
+  </si>
+  <si>
+    <t>HealthcareService.active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>Whether this HealthcareService record is in active use</t>
+  </si>
+  <si>
+    <t>This flag is used to mark the record to not be used. This is not used when a center is closed for maintenance, or for holidays, the notAvailable period is to be used for this.</t>
+  </si>
+  <si>
+    <t>This element is labeled as a modifier because it may be used to mark that the resource was created in error.</t>
+  </si>
+  <si>
+    <t>This resource is generally assumed to be active if no value is provided for the active element</t>
+  </si>
+  <si>
+    <t>.statusCode</t>
+  </si>
+  <si>
+    <t>FiveWs.status</t>
+  </si>
+  <si>
+    <t>HealthcareService.providedBy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Organization)
+</t>
+  </si>
+  <si>
+    <t>Référence vers la structure FINESS ET</t>
+  </si>
+  <si>
+    <t>The organization that provides this healthcare service.</t>
+  </si>
+  <si>
+    <t>Reference vers l'id de la ressource de la structure FINESS ET à laquelle est rattaché cette activité sanitaire</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
+  </si>
+  <si>
+    <t>.scopingRole.Organization</t>
+  </si>
+  <si>
+    <t>HealthcareService.category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">service category
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Broad category of service being performed or delivered</t>
+  </si>
+  <si>
+    <t>Identifies the broad category of service being performed or delivered.</t>
+  </si>
+  <si>
+    <t>Selecting a Service Category then determines the list of relevant service types that can be selected in the primary service type.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>Modalité de l'activité de soins</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J132-ModaliteActivite-RASS/FHIR/JDV-J132-ModaliteActivite-RASS</t>
+  </si>
+  <si>
+    <t>.code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>HealthcareService.type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">service type
+</t>
+  </si>
+  <si>
+    <t>Type of service that may be delivered or performed</t>
+  </si>
+  <si>
+    <t>The specific type of service that may be delivered or performed.</t>
+  </si>
+  <si>
+    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
+  </si>
+  <si>
+    <t>Code définissant l'activité de soins autorisée</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J133-ActiviteSanitaireRegulee-RASS/FHIR/JDV-J133-ActiviteSanitaireRegulee-RASS</t>
+  </si>
+  <si>
+    <t>.actrelationship[typeCode=COMP.act[classCode=ACT][moodCode=DEF].code</t>
+  </si>
+  <si>
+    <t>HealthcareService.specialty</t>
+  </si>
+  <si>
+    <t>Specialties handled by the HealthcareService</t>
+  </si>
+  <si>
+    <t>Collection of specialties handled by the service site. This is more of a medical term.</t>
+  </si>
+  <si>
+    <t>A specialty that a healthcare service may provide.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/c80-practice-codes</t>
+  </si>
+  <si>
+    <t>HealthcareService.location</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Location)
+</t>
+  </si>
+  <si>
+    <t>Location(s) where service may be provided</t>
+  </si>
+  <si>
+    <t>The location(s) where this healthcare service may be provided.</t>
+  </si>
+  <si>
+    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
+  </si>
+  <si>
+    <t>.location.role[classCode=SDLOC]</t>
+  </si>
+  <si>
+    <t>FiveWs.where[x]</t>
+  </si>
+  <si>
+    <t>HealthcareService.name</t>
   </si>
   <si>
     <t xml:space="preserve">string
 </t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>HealthcareService.meta.extension</t>
-  </si>
-  <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>HealthcareService.meta.versionId</t>
-  </si>
-  <si>
-    <t>Version specific identifier</t>
-  </si>
-  <si>
-    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
-  </si>
-  <si>
-    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
-  </si>
-  <si>
-    <t>Meta.versionId</t>
-  </si>
-  <si>
-    <t>HealthcareService.meta.lastUpdated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">instant
-</t>
-  </si>
-  <si>
-    <t>When the resource version last changed</t>
-  </si>
-  <si>
-    <t>When the resource last changed - e.g. when the version changed.</t>
-  </si>
-  <si>
-    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
-  </si>
-  <si>
-    <t>Meta.lastUpdated</t>
-  </si>
-  <si>
-    <t>HealthcareService.meta.source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">uri
-</t>
-  </si>
-  <si>
-    <t>Identifies where the resource comes from</t>
-  </si>
-  <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
-  </si>
-  <si>
-    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
-This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
-  </si>
-  <si>
-    <t>Meta.source</t>
-  </si>
-  <si>
-    <t>HealthcareService.meta.profile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
-</t>
-  </si>
-  <si>
-    <t>Profiles this resource claims to conform to</t>
-  </si>
-  <si>
-    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
-  </si>
-  <si>
-    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
-  </si>
-  <si>
-    <t>Meta.profile</t>
-  </si>
-  <si>
-    <t>HealthcareService.meta.security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Security Labels applied to this resource</t>
-  </si>
-  <si>
-    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
-  </si>
-  <si>
-    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
-  </si>
-  <si>
-    <t>Meta.security</t>
-  </si>
-  <si>
-    <t>CV</t>
-  </si>
-  <si>
-    <t>HealthcareService.meta.tag</t>
-  </si>
-  <si>
-    <t>Tags applied to this resource</t>
-  </si>
-  <si>
-    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
-  </si>
-  <si>
-    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
-  </si>
-  <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
-  </si>
-  <si>
-    <t>Meta.tag</t>
-  </si>
-  <si>
-    <t>HealthcareService.implicitRules</t>
-  </si>
-  <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
-  </si>
-  <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
-  </si>
-  <si>
-    <t>Resource.implicitRules</t>
-  </si>
-  <si>
-    <t>HealthcareService.language</t>
-  </si>
-  <si>
-    <t xml:space="preserve">code
-</t>
-  </si>
-  <si>
-    <t>Language of the resource content</t>
-  </si>
-  <si>
-    <t>The base language in which the resource is written.</t>
-  </si>
-  <si>
-    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
-  </si>
-  <si>
-    <t>preferred</t>
-  </si>
-  <si>
-    <t>A human language.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
-  </si>
-  <si>
-    <t>Resource.language</t>
-  </si>
-  <si>
-    <t>HealthcareService.text</t>
-  </si>
-  <si>
-    <t>narrative
-htmlxhtmldisplay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narrative
-</t>
-  </si>
-  <si>
-    <t>Text summary of the resource, for human interpretation</t>
-  </si>
-  <si>
-    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
-  </si>
-  <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
-  </si>
-  <si>
-    <t>DomainResource.text</t>
-  </si>
-  <si>
-    <t>Act.text?</t>
-  </si>
-  <si>
-    <t>HealthcareService.contained</t>
-  </si>
-  <si>
-    <t>inline resources
-anonymous resourcescontained resources</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resource
-</t>
-  </si>
-  <si>
-    <t>Contained, inline Resources</t>
-  </si>
-  <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
-  </si>
-  <si>
-    <t>DomainResource.contained</t>
-  </si>
-  <si>
-    <t>HealthcareService.extension</t>
-  </si>
-  <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>HealthcareService.extension:activityType</t>
-  </si>
-  <si>
-    <t>activityType</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/HealthcareService-activityType}
-</t>
-  </si>
-  <si>
-    <t>Optional Extensions Element</t>
-  </si>
-  <si>
-    <t>Optional Extension Element - found in all resources.</t>
-  </si>
-  <si>
-    <t>HealthcareService.extension:authorizationDate</t>
-  </si>
-  <si>
-    <t>authorizationDate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/HealthcareService-authorizationDate}
-</t>
-  </si>
-  <si>
-    <t>HealthcareService.extension:authorizationNumberARHGOS</t>
-  </si>
-  <si>
-    <t>authorizationNumberARHGOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/HealthcareService-authorizationNumberARHGOS}
-</t>
-  </si>
-  <si>
-    <t>HealthcareService.extension:implementationPeriod</t>
-  </si>
-  <si>
-    <t>implementationPeriod</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/HealthcareService-implementationPeriod}
-</t>
-  </si>
-  <si>
-    <t>HealthcareService.extension:deleteAutorisationImplantation</t>
-  </si>
-  <si>
-    <t>deleteAutorisationImplantation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/HealthcareService-deleteAutorisationImplantation}
-</t>
-  </si>
-  <si>
-    <t>HealthcareService.extension:dateUpdateActivity</t>
-  </si>
-  <si>
-    <t>dateUpdateActivity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/HealthcareService-dateUpdateActivity}
-</t>
-  </si>
-  <si>
-    <t>HealthcareService.modifierExtension</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
-  </si>
-  <si>
-    <t>DomainResource.modifierExtension</t>
-  </si>
-  <si>
-    <t>HealthcareService.identifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifier
-</t>
-  </si>
-  <si>
-    <t>Numéro autorisation ARGHOS</t>
-  </si>
-  <si>
-    <t>External identifiers for this item.</t>
-  </si>
-  <si>
-    <t>.id</t>
-  </si>
-  <si>
-    <t>FiveWs.identifier</t>
-  </si>
-  <si>
-    <t>HealthcareService.active</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>Whether this HealthcareService record is in active use</t>
-  </si>
-  <si>
-    <t>This flag is used to mark the record to not be used. This is not used when a center is closed for maintenance, or for holidays, the notAvailable period is to be used for this.</t>
-  </si>
-  <si>
-    <t>This element is labeled as a modifier because it may be used to mark that the resource was created in error.</t>
-  </si>
-  <si>
-    <t>This resource is generally assumed to be active if no value is provided for the active element</t>
-  </si>
-  <si>
-    <t>.statusCode</t>
-  </si>
-  <si>
-    <t>FiveWs.status</t>
-  </si>
-  <si>
-    <t>HealthcareService.providedBy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Organization)
-</t>
-  </si>
-  <si>
-    <t>Référence vers la structure FINESS ET</t>
-  </si>
-  <si>
-    <t>The organization that provides this healthcare service.</t>
-  </si>
-  <si>
-    <t>Reference vers l'id de la ressource de la structure FINESS ET à laquelle est rattaché cette activité sanitaire</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
-  </si>
-  <si>
-    <t>.scopingRole.Organization</t>
-  </si>
-  <si>
-    <t>HealthcareService.category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">service category
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
-    <t>Broad category of service being performed or delivered</t>
-  </si>
-  <si>
-    <t>Identifies the broad category of service being performed or delivered.</t>
-  </si>
-  <si>
-    <t>Selecting a Service Category then determines the list of relevant service types that can be selected in the primary service type.</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>Modalité de l'activité de soins</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J132-ModaliteActivite-RASS/FHIR/JDV-J132-ModaliteActivite-RASS</t>
-  </si>
-  <si>
-    <t>.code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>HealthcareService.type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">service type
-</t>
-  </si>
-  <si>
-    <t>Type of service that may be delivered or performed</t>
-  </si>
-  <si>
-    <t>The specific type of service that may be delivered or performed.</t>
-  </si>
-  <si>
-    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
-  </si>
-  <si>
-    <t>Code définissant l'activité de soins autorisée</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J133-ActiviteSanitaireRegulee-RASS/FHIR/JDV-J133-ActiviteSanitaireRegulee-RASS</t>
-  </si>
-  <si>
-    <t>.actrelationship[typeCode=COMP.act[classCode=ACT][moodCode=DEF].code</t>
-  </si>
-  <si>
-    <t>HealthcareService.specialty</t>
-  </si>
-  <si>
-    <t>Specialties handled by the HealthcareService</t>
-  </si>
-  <si>
-    <t>Collection of specialties handled by the service site. This is more of a medical term.</t>
-  </si>
-  <si>
-    <t>A specialty that a healthcare service may provide.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/c80-practice-codes</t>
-  </si>
-  <si>
-    <t>HealthcareService.location</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Location)
-</t>
-  </si>
-  <si>
-    <t>Location(s) where service may be provided</t>
-  </si>
-  <si>
-    <t>The location(s) where this healthcare service may be provided.</t>
-  </si>
-  <si>
-    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
-  </si>
-  <si>
-    <t>.location.role[classCode=SDLOC]</t>
-  </si>
-  <si>
-    <t>FiveWs.where[x]</t>
-  </si>
-  <si>
-    <t>HealthcareService.name</t>
-  </si>
-  <si>
     <t>Description of service as presented to a consumer while searching</t>
   </si>
   <si>
@@ -964,6 +819,9 @@
     <t>The provision means being commissioned by, contractually obliged or financially sourced. Types of costings that may apply to this healthcare service, such if the service may be available for free, some discounts available, or fees apply.</t>
   </si>
   <si>
+    <t>example</t>
+  </si>
+  <si>
     <t>http://hl7.org/fhir/ValueSet/service-provision-conditions</t>
   </si>
   <si>
@@ -986,7 +844,25 @@
     <t>HealthcareService.eligibility.id</t>
   </si>
   <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
     <t>HealthcareService.eligibility.extension</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
   </si>
   <si>
     <t>HealthcareService.eligibility.modifierExtension</t>
@@ -1383,6 +1259,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -1548,7 +1439,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL65"/>
+  <dimension ref="A1:AL57"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="56.546875" customWidth="true" bestFit="true"/>
@@ -1575,7 +1466,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="87.19921875" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="109.73046875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
@@ -1706,7 +1597,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>28</v>
       </c>
@@ -1812,7 +1703,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>80</v>
       </c>
@@ -1920,7 +1811,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>88</v>
       </c>
@@ -2026,7 +1917,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>96</v>
       </c>
@@ -2048,10 +1939,10 @@
         <v>73</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K5" t="s" s="2">
         <v>97</v>
@@ -2062,7 +1953,9 @@
       <c r="M5" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="N5" s="2"/>
+      <c r="N5" t="s" s="2">
+        <v>100</v>
+      </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
         <v>73</v>
@@ -2111,7 +2004,7 @@
         <v>73</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>74</v>
@@ -2120,35 +2013,35 @@
         <v>81</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AL5" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>73</v>
@@ -2195,28 +2088,28 @@
         <v>73</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>73</v>
+        <v>109</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="AC6" t="s" s="2">
-        <v>109</v>
+        <v>73</v>
       </c>
       <c r="AD6" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="AF6" t="s" s="2">
         <v>111</v>
@@ -2225,31 +2118,31 @@
         <v>74</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ6" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AK6" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AL6" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7" hidden="true">
+      <c r="A7" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="AK6" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AL6" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="2">
-        <v>113</v>
-      </c>
       <c r="B7" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>73</v>
+        <v>113</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2265,19 +2158,19 @@
         <v>73</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2327,7 +2220,7 @@
         <v>73</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>74</v>
@@ -2342,29 +2235,29 @@
         <v>94</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AL7" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>73</v>
+        <v>121</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>73</v>
@@ -2373,19 +2266,19 @@
         <v>73</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2435,33 +2328,33 @@
         <v>73</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="AL8" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2469,10 +2362,10 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>73</v>
@@ -2481,20 +2374,18 @@
         <v>73</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>128</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>73</v>
@@ -2531,47 +2422,49 @@
         <v>73</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>73</v>
+        <v>131</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>73</v>
+        <v>132</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>73</v>
+        <v>133</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>94</v>
+        <v>135</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="AL9" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="C10" s="2"/>
+        <v>127</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="D10" t="s" s="2">
         <v>73</v>
       </c>
@@ -2580,7 +2473,7 @@
         <v>74</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>73</v>
@@ -2589,20 +2482,18 @@
         <v>73</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>134</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="N10" s="2"/>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>73</v>
@@ -2651,7 +2542,7 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
@@ -2663,23 +2554,25 @@
         <v>93</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>94</v>
+        <v>135</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="AL10" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="C11" s="2"/>
+        <v>127</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="D11" t="s" s="2">
         <v>73</v>
       </c>
@@ -2688,7 +2581,7 @@
         <v>74</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>73</v>
@@ -2697,20 +2590,18 @@
         <v>73</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="N11" t="s" s="2">
         <v>140</v>
       </c>
+      <c r="N11" s="2"/>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>73</v>
@@ -2735,13 +2626,13 @@
         <v>73</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>141</v>
+        <v>73</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>142</v>
+        <v>73</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>143</v>
+        <v>73</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>73</v>
@@ -2759,7 +2650,7 @@
         <v>73</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>74</v>
@@ -2771,32 +2662,34 @@
         <v>93</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>94</v>
+        <v>135</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" hidden="true">
+      <c r="A12" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="C12" t="s" s="2">
         <v>145</v>
       </c>
-      <c r="AL11" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
         <v>73</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>73</v>
@@ -2805,20 +2698,18 @@
         <v>73</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>149</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>73</v>
@@ -2843,13 +2734,13 @@
         <v>73</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>150</v>
+        <v>73</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>151</v>
+        <v>73</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>152</v>
+        <v>73</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>73</v>
@@ -2867,7 +2758,7 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
@@ -2879,23 +2770,25 @@
         <v>93</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>94</v>
+        <v>135</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>145</v>
+        <v>95</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="C13" s="2"/>
+        <v>127</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="D13" t="s" s="2">
         <v>73</v>
       </c>
@@ -2904,29 +2797,27 @@
         <v>74</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>73</v>
@@ -2975,35 +2866,37 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>94</v>
+        <v>135</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="C14" s="2"/>
+        <v>127</v>
+      </c>
+      <c r="C14" t="s" s="2">
+        <v>151</v>
+      </c>
       <c r="D14" t="s" s="2">
         <v>73</v>
       </c>
@@ -3024,17 +2917,15 @@
         <v>73</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>73</v>
@@ -3059,13 +2950,13 @@
         <v>73</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>164</v>
+        <v>73</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>165</v>
+        <v>73</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>166</v>
+        <v>73</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>73</v>
@@ -3083,44 +2974,46 @@
         <v>73</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>167</v>
+        <v>134</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>94</v>
+        <v>135</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="C15" s="2"/>
+        <v>127</v>
+      </c>
+      <c r="C15" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="D15" t="s" s="2">
-        <v>169</v>
+        <v>73</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>73</v>
@@ -3132,17 +3025,15 @@
         <v>73</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>171</v>
+        <v>139</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>173</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>73</v>
@@ -3191,67 +3082,69 @@
         <v>73</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>174</v>
+        <v>134</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>94</v>
+        <v>135</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>175</v>
+        <v>95</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="J16" t="s" s="2">
         <v>73</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>178</v>
+        <v>128</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>179</v>
+        <v>158</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>180</v>
+        <v>159</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="O16" s="2"/>
+        <v>160</v>
+      </c>
+      <c r="O16" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="P16" t="s" s="2">
         <v>73</v>
       </c>
@@ -3287,19 +3180,19 @@
         <v>73</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>73</v>
+        <v>131</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>73</v>
+        <v>132</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>73</v>
+        <v>133</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>182</v>
+        <v>162</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>74</v>
@@ -3308,10 +3201,10 @@
         <v>75</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>73</v>
+        <v>135</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>95</v>
@@ -3320,12 +3213,12 @@
         <v>73</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>183</v>
+        <v>163</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>183</v>
+        <v>163</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3333,7 +3226,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>75</v>
@@ -3345,16 +3238,16 @@
         <v>73</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>104</v>
+        <v>164</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3393,19 +3286,19 @@
         <v>73</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>109</v>
+        <v>73</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>186</v>
+        <v>163</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>74</v>
@@ -3417,25 +3310,23 @@
         <v>93</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>73</v>
+        <v>167</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>73</v>
+        <v>168</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="C18" t="s" s="2">
-        <v>188</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
         <v>73</v>
       </c>
@@ -3450,26 +3341,30 @@
         <v>73</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N18" s="2"/>
+        <v>172</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>173</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="Q18" s="2"/>
+      <c r="Q18" t="s" s="2">
+        <v>174</v>
+      </c>
       <c r="R18" t="s" s="2">
         <v>73</v>
       </c>
@@ -3513,37 +3408,35 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>186</v>
+        <v>169</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>95</v>
+        <v>175</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>73</v>
+        <v>176</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="C19" t="s" s="2">
-        <v>193</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
         <v>73</v>
       </c>
@@ -3561,18 +3454,20 @@
         <v>73</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>194</v>
+        <v>178</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>180</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>181</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>73</v>
@@ -3621,46 +3516,44 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>112</v>
+        <v>182</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>95</v>
+        <v>183</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="C20" t="s" s="2">
-        <v>196</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>73</v>
+        <v>185</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>73</v>
@@ -3669,18 +3562,20 @@
         <v>73</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N20" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>189</v>
+      </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>73</v>
@@ -3705,13 +3600,13 @@
         <v>73</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>73</v>
+        <v>190</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>73</v>
+        <v>191</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>73</v>
+        <v>192</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>73</v>
@@ -3729,7 +3624,7 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>74</v>
@@ -3741,34 +3636,32 @@
         <v>93</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>95</v>
+        <v>193</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>73</v>
+        <v>194</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="C21" t="s" s="2">
-        <v>199</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>73</v>
+        <v>196</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>73</v>
@@ -3777,18 +3670,20 @@
         <v>73</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N21" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>73</v>
@@ -3813,13 +3708,13 @@
         <v>73</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>73</v>
+        <v>190</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>73</v>
+        <v>200</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>73</v>
+        <v>201</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>73</v>
@@ -3837,7 +3732,7 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>74</v>
@@ -3849,25 +3744,23 @@
         <v>93</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>95</v>
+        <v>202</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="C22" t="s" s="2">
-        <v>202</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
         <v>73</v>
       </c>
@@ -3876,27 +3769,29 @@
         <v>74</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>203</v>
+        <v>186</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>205</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>73</v>
@@ -3921,13 +3816,13 @@
         <v>73</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>73</v>
+        <v>206</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>73</v>
+        <v>207</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>73</v>
@@ -3945,7 +3840,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>74</v>
@@ -3957,25 +3852,23 @@
         <v>93</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>95</v>
+        <v>202</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="C23" t="s" s="2">
-        <v>205</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
         <v>73</v>
       </c>
@@ -3984,27 +3877,29 @@
         <v>74</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N23" s="2"/>
+        <v>211</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>73</v>
@@ -4053,7 +3948,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
@@ -4065,57 +3960,55 @@
         <v>93</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>112</v>
+        <v>182</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>95</v>
+        <v>213</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>73</v>
+        <v>214</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J24" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="J24" t="s" s="2">
-        <v>73</v>
-      </c>
       <c r="K24" t="s" s="2">
-        <v>104</v>
+        <v>216</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>210</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>73</v>
       </c>
@@ -4151,45 +4044,45 @@
         <v>73</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>109</v>
+        <v>73</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>95</v>
+        <v>220</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4200,10 +4093,10 @@
         <v>74</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>73</v>
@@ -4212,15 +4105,17 @@
         <v>82</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>223</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>73</v>
@@ -4269,13 +4164,13 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>93</v>
@@ -4284,18 +4179,18 @@
         <v>94</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>217</v>
+        <v>73</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4309,33 +4204,31 @@
         <v>81</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="Q26" t="s" s="2">
-        <v>223</v>
-      </c>
+      <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
         <v>73</v>
       </c>
@@ -4379,7 +4272,7 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>74</v>
@@ -4394,18 +4287,18 @@
         <v>94</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>225</v>
+        <v>73</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4419,7 +4312,7 @@
         <v>81</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>73</v>
@@ -4428,16 +4321,16 @@
         <v>82</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4487,7 +4380,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>
@@ -4499,25 +4392,25 @@
         <v>93</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>234</v>
+        <v>73</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4527,25 +4420,25 @@
         <v>75</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4571,31 +4464,31 @@
         <v>73</v>
       </c>
       <c r="X28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF28" t="s" s="2">
         <v>239</v>
-      </c>
-      <c r="Y28" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="Z28" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="AA28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
@@ -4607,25 +4500,25 @@
         <v>93</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>94</v>
+        <v>244</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>243</v>
+        <v>73</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>245</v>
+        <v>73</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -4635,25 +4528,25 @@
         <v>75</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>235</v>
+        <v>209</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4679,13 +4572,13 @@
         <v>73</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>239</v>
+        <v>73</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>249</v>
+        <v>73</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>250</v>
+        <v>73</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>73</v>
@@ -4703,7 +4596,7 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
@@ -4715,21 +4608,21 @@
         <v>93</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>94</v>
+        <v>182</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="30" hidden="true">
+      <c r="A30" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="AL29" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s" s="2">
-        <v>252</v>
-      </c>
       <c r="B30" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4740,28 +4633,28 @@
         <v>74</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>235</v>
+        <v>186</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>248</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4787,10 +4680,10 @@
         <v>73</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>164</v>
+        <v>255</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="Z30" t="s" s="2">
         <v>256</v>
@@ -4811,7 +4704,7 @@
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
@@ -4826,18 +4719,18 @@
         <v>94</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4848,29 +4741,27 @@
         <v>74</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="N31" t="s" s="2">
         <v>261</v>
       </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>73</v>
@@ -4919,7 +4810,7 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
@@ -4931,21 +4822,21 @@
         <v>93</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>231</v>
+        <v>94</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="32" hidden="true">
+      <c r="A32" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="AL31" t="s" s="2">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s" s="2">
-        <v>264</v>
-      </c>
       <c r="B32" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4956,7 +4847,7 @@
         <v>74</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>73</v>
@@ -4965,20 +4856,18 @@
         <v>73</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>97</v>
+        <v>216</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>264</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>73</v>
@@ -5027,7 +4916,7 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>74</v>
@@ -5036,35 +4925,35 @@
         <v>81</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>268</v>
+        <v>102</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>73</v>
+        <v>157</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>73</v>
@@ -5073,19 +4962,19 @@
         <v>73</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>97</v>
+        <v>128</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>272</v>
+        <v>160</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5123,16 +5012,16 @@
         <v>73</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>73</v>
+        <v>131</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>73</v>
+        <v>132</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>73</v>
+        <v>133</v>
       </c>
       <c r="AF33" t="s" s="2">
         <v>269</v>
@@ -5141,61 +5030,63 @@
         <v>74</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>94</v>
+        <v>135</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>273</v>
+        <v>95</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>73</v>
+        <v>271</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>275</v>
+        <v>128</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="O34" s="2"/>
+        <v>160</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>73</v>
       </c>
@@ -5249,27 +5140,27 @@
         <v>74</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>94</v>
+        <v>135</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>279</v>
+        <v>95</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5280,7 +5171,7 @@
         <v>74</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>73</v>
@@ -5289,19 +5180,19 @@
         <v>73</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>281</v>
+        <v>186</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>284</v>
+        <v>199</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5327,10 +5218,10 @@
         <v>73</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>73</v>
+        <v>255</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>73</v>
+        <v>278</v>
       </c>
       <c r="Z35" t="s" s="2">
         <v>73</v>
@@ -5351,7 +5242,7 @@
         <v>73</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>74</v>
@@ -5363,21 +5254,21 @@
         <v>93</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>285</v>
+        <v>94</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>286</v>
+        <v>257</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5388,7 +5279,7 @@
         <v>74</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>73</v>
@@ -5400,16 +5291,16 @@
         <v>73</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>288</v>
+        <v>227</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5459,33 +5350,33 @@
         <v>73</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>292</v>
+        <v>94</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5496,10 +5387,10 @@
         <v>74</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>73</v>
@@ -5508,16 +5399,16 @@
         <v>73</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>258</v>
+        <v>186</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5543,13 +5434,13 @@
         <v>73</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>73</v>
+        <v>255</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>73</v>
+        <v>288</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>73</v>
+        <v>289</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>73</v>
@@ -5567,7 +5458,7 @@
         <v>73</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>74</v>
@@ -5579,21 +5470,21 @@
         <v>93</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>231</v>
+        <v>94</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5604,7 +5495,7 @@
         <v>74</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>73</v>
@@ -5616,16 +5507,16 @@
         <v>73</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>235</v>
+        <v>186</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5651,13 +5542,13 @@
         <v>73</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>73</v>
@@ -5675,7 +5566,7 @@
         <v>73</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>74</v>
@@ -5690,18 +5581,18 @@
         <v>94</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>304</v>
+        <v>290</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5712,10 +5603,10 @@
         <v>74</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>73</v>
@@ -5724,15 +5615,17 @@
         <v>73</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>306</v>
+        <v>186</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>299</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>300</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>73</v>
@@ -5757,13 +5650,13 @@
         <v>73</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>73</v>
+        <v>109</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>73</v>
@@ -5781,7 +5674,7 @@
         <v>73</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>74</v>
@@ -5796,18 +5689,18 @@
         <v>94</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>101</v>
+        <v>301</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5818,10 +5711,10 @@
         <v>74</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>73</v>
@@ -5830,15 +5723,17 @@
         <v>73</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>97</v>
+        <v>186</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>98</v>
+        <v>303</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>304</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>73</v>
@@ -5863,13 +5758,13 @@
         <v>73</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>73</v>
+        <v>255</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>73</v>
+        <v>305</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>73</v>
+        <v>306</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>73</v>
@@ -5887,47 +5782,47 @@
         <v>73</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>100</v>
+        <v>302</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>101</v>
+        <v>290</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>73</v>
@@ -5936,17 +5831,15 @@
         <v>73</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>104</v>
+        <v>170</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>105</v>
+        <v>308</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>73</v>
@@ -5983,49 +5876,49 @@
         <v>73</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>109</v>
+        <v>73</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>111</v>
+        <v>307</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>95</v>
+        <v>290</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>312</v>
+        <v>73</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6035,29 +5928,27 @@
         <v>75</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>104</v>
+        <v>259</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="N42" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="M42" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>210</v>
-      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>73</v>
       </c>
@@ -6105,7 +5996,7 @@
         <v>73</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>74</v>
@@ -6117,21 +6008,21 @@
         <v>93</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>95</v>
+        <v>314</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6154,17 +6045,15 @@
         <v>73</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>235</v>
+        <v>216</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>317</v>
+        <v>263</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>248</v>
-      </c>
+        <v>264</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>73</v>
@@ -6189,10 +6078,10 @@
         <v>73</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>150</v>
+        <v>73</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>319</v>
+        <v>73</v>
       </c>
       <c r="Z43" t="s" s="2">
         <v>73</v>
@@ -6213,7 +6102,7 @@
         <v>73</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>316</v>
+        <v>265</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>74</v>
@@ -6222,35 +6111,35 @@
         <v>81</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>304</v>
+        <v>102</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>73</v>
+        <v>157</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>73</v>
@@ -6262,16 +6151,16 @@
         <v>73</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>275</v>
+        <v>128</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>321</v>
+        <v>267</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>322</v>
+        <v>268</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>323</v>
+        <v>160</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6309,79 +6198,81 @@
         <v>73</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>73</v>
+        <v>131</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>73</v>
+        <v>132</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>73</v>
+        <v>133</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>320</v>
+        <v>269</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>94</v>
+        <v>135</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>324</v>
+        <v>95</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>73</v>
+        <v>271</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>235</v>
+        <v>128</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>326</v>
+        <v>272</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>327</v>
+        <v>273</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="O45" s="2"/>
+        <v>160</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>73</v>
       </c>
@@ -6405,13 +6296,13 @@
         <v>73</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>150</v>
+        <v>73</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>329</v>
+        <v>73</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>330</v>
+        <v>73</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>73</v>
@@ -6429,7 +6320,7 @@
         <v>73</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>325</v>
+        <v>274</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>74</v>
@@ -6441,21 +6332,21 @@
         <v>93</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>94</v>
+        <v>135</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>331</v>
+        <v>95</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>332</v>
+        <v>318</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>332</v>
+        <v>318</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6478,16 +6369,16 @@
         <v>73</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>235</v>
+        <v>104</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>333</v>
+        <v>319</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>334</v>
+        <v>320</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>335</v>
+        <v>219</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6513,13 +6404,13 @@
         <v>73</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>239</v>
+        <v>190</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>336</v>
+        <v>321</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>73</v>
@@ -6537,7 +6428,7 @@
         <v>73</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>332</v>
+        <v>318</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>74</v>
@@ -6552,18 +6443,18 @@
         <v>94</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>331</v>
+        <v>314</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>338</v>
+        <v>323</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>338</v>
+        <v>323</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6574,7 +6465,7 @@
         <v>74</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>73</v>
@@ -6586,17 +6477,15 @@
         <v>73</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>235</v>
+        <v>170</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>339</v>
+        <v>324</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>341</v>
-      </c>
+        <v>325</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>73</v>
@@ -6621,13 +6510,13 @@
         <v>73</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>164</v>
+        <v>73</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>165</v>
+        <v>73</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>166</v>
+        <v>73</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>73</v>
@@ -6645,13 +6534,13 @@
         <v>73</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>338</v>
+        <v>323</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>93</v>
@@ -6660,18 +6549,18 @@
         <v>94</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>342</v>
+        <v>314</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6682,7 +6571,7 @@
         <v>74</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>73</v>
@@ -6694,16 +6583,16 @@
         <v>73</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>235</v>
+        <v>327</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>344</v>
+        <v>328</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>345</v>
+        <v>329</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>248</v>
+        <v>330</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6729,13 +6618,13 @@
         <v>73</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>150</v>
+        <v>73</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>346</v>
+        <v>73</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>347</v>
+        <v>73</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>73</v>
@@ -6753,13 +6642,13 @@
         <v>73</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>93</v>
@@ -6768,18 +6657,18 @@
         <v>94</v>
       </c>
       <c r="AK48" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="49" hidden="true">
+      <c r="A49" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="AL48" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s" s="2">
-        <v>348</v>
-      </c>
       <c r="B49" t="s" s="2">
-        <v>348</v>
+        <v>331</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6790,7 +6679,7 @@
         <v>74</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>73</v>
@@ -6802,15 +6691,17 @@
         <v>73</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>219</v>
+        <v>327</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>349</v>
+        <v>332</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>333</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>330</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>73</v>
@@ -6859,7 +6750,7 @@
         <v>73</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>348</v>
+        <v>331</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>74</v>
@@ -6874,18 +6765,18 @@
         <v>94</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>331</v>
+        <v>314</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>351</v>
+        <v>334</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>351</v>
+        <v>334</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6896,10 +6787,10 @@
         <v>74</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>73</v>
@@ -6908,17 +6799,15 @@
         <v>73</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>306</v>
+        <v>259</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>352</v>
+        <v>335</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>354</v>
-      </c>
+        <v>336</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>73</v>
@@ -6967,7 +6856,7 @@
         <v>73</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>351</v>
+        <v>334</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>74</v>
@@ -6982,18 +6871,18 @@
         <v>94</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>355</v>
+        <v>314</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>356</v>
+        <v>337</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>356</v>
+        <v>337</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7016,13 +6905,13 @@
         <v>73</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>97</v>
+        <v>216</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>98</v>
+        <v>263</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>99</v>
+        <v>264</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7073,7 +6962,7 @@
         <v>73</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>100</v>
+        <v>265</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>74</v>
@@ -7088,22 +6977,22 @@
         <v>73</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>357</v>
+        <v>338</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>357</v>
+        <v>338</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>103</v>
+        <v>157</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7122,16 +7011,16 @@
         <v>73</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>105</v>
+        <v>267</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>106</v>
+        <v>268</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>107</v>
+        <v>160</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7169,19 +7058,19 @@
         <v>73</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>111</v>
+        <v>269</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>74</v>
@@ -7193,7 +7082,7 @@
         <v>93</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>95</v>
@@ -7202,16 +7091,16 @@
         <v>73</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>358</v>
+        <v>339</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>358</v>
+        <v>339</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>312</v>
+        <v>271</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -7230,19 +7119,19 @@
         <v>82</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>313</v>
+        <v>272</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>314</v>
+        <v>273</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>107</v>
+        <v>160</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>210</v>
+        <v>161</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>73</v>
@@ -7291,7 +7180,7 @@
         <v>73</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>315</v>
+        <v>274</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>74</v>
@@ -7303,7 +7192,7 @@
         <v>93</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>95</v>
@@ -7312,12 +7201,12 @@
         <v>73</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>359</v>
+        <v>340</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>359</v>
+        <v>340</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7325,10 +7214,10 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>73</v>
@@ -7340,16 +7229,16 @@
         <v>73</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>160</v>
+        <v>216</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>360</v>
+        <v>341</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>361</v>
+        <v>342</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>267</v>
+        <v>219</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7375,13 +7264,13 @@
         <v>73</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>239</v>
+        <v>73</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>362</v>
+        <v>73</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>363</v>
+        <v>73</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>73</v>
@@ -7399,13 +7288,13 @@
         <v>73</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>359</v>
+        <v>340</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>93</v>
@@ -7414,18 +7303,18 @@
         <v>94</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>355</v>
+        <v>102</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>364</v>
+        <v>343</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>364</v>
+        <v>343</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7448,15 +7337,17 @@
         <v>73</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>219</v>
+        <v>344</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>365</v>
+        <v>345</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>346</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>347</v>
+      </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>73</v>
@@ -7505,7 +7396,7 @@
         <v>73</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>364</v>
+        <v>343</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>74</v>
@@ -7517,21 +7408,21 @@
         <v>93</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>94</v>
+        <v>348</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>355</v>
+        <v>314</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>367</v>
+        <v>349</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>367</v>
+        <v>349</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7545,7 +7436,7 @@
         <v>81</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>73</v>
@@ -7554,16 +7445,16 @@
         <v>73</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>368</v>
+        <v>216</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>369</v>
+        <v>350</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>370</v>
+        <v>351</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>371</v>
+        <v>219</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -7613,7 +7504,7 @@
         <v>73</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>367</v>
+        <v>349</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>74</v>
@@ -7628,18 +7519,18 @@
         <v>94</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>355</v>
+        <v>314</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>372</v>
+        <v>352</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>372</v>
+        <v>352</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7650,10 +7541,10 @@
         <v>74</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>73</v>
@@ -7662,16 +7553,16 @@
         <v>73</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>368</v>
+        <v>353</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>373</v>
+        <v>354</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>374</v>
+        <v>355</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>371</v>
+        <v>212</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -7721,890 +7612,46 @@
         <v>73</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>372</v>
+        <v>352</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>94</v>
+        <v>182</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="B58" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="C58" s="2"/>
-      <c r="D58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E58" s="2"/>
-      <c r="F58" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G58" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K58" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
-      <c r="P58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q58" s="2"/>
-      <c r="R58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF58" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="AG58" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH58" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI58" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ58" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK58" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="C59" s="2"/>
-      <c r="D59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E59" s="2"/>
-      <c r="F59" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K59" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="L59" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
-      <c r="P59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q59" s="2"/>
-      <c r="R59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AG59" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AK59" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="C60" s="2"/>
-      <c r="D60" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="E60" s="2"/>
-      <c r="F60" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G60" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K60" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L60" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="O60" s="2"/>
-      <c r="P60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q60" s="2"/>
-      <c r="R60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="AG60" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH60" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI60" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ60" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="AK60" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="C61" s="2"/>
-      <c r="D61" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="E61" s="2"/>
-      <c r="F61" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G61" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K61" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L61" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="P61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q61" s="2"/>
-      <c r="R61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="AG61" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH61" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI61" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ61" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="AK61" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="C62" s="2"/>
-      <c r="D62" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E62" s="2"/>
-      <c r="F62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H62" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I62" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J62" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K62" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="L62" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="O62" s="2"/>
-      <c r="P62" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q62" s="2"/>
-      <c r="R62" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S62" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T62" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U62" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V62" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W62" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X62" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y62" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z62" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA62" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="AG62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI62" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ62" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK62" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="C63" s="2"/>
-      <c r="D63" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E63" s="2"/>
-      <c r="F63" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H63" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I63" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J63" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K63" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="L63" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="O63" s="2"/>
-      <c r="P63" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q63" s="2"/>
-      <c r="R63" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S63" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T63" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U63" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V63" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W63" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X63" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z63" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="AG63" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI63" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ63" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="AK63" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="C64" s="2"/>
-      <c r="D64" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E64" s="2"/>
-      <c r="F64" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G64" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H64" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I64" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J64" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K64" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="O64" s="2"/>
-      <c r="P64" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q64" s="2"/>
-      <c r="R64" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S64" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T64" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U64" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V64" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W64" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X64" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y64" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z64" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA64" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB64" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD64" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE64" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF64" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="AG64" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI64" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ64" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK64" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="C65" s="2"/>
-      <c r="D65" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E65" s="2"/>
-      <c r="F65" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G65" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H65" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I65" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J65" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K65" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="L65" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="O65" s="2"/>
-      <c r="P65" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q65" s="2"/>
-      <c r="R65" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S65" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T65" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U65" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V65" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W65" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X65" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z65" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="AG65" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH65" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI65" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ65" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="AK65" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="AL65" t="s" s="2">
         <v>73</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AL57">
+    <filterColumn colId="6">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="26">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI56">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-12T10:08:35+00:00</t>
+    <t>2023-04-12T14:03:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-12T14:03:54+00:00</t>
+    <t>2023-04-13T07:49:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T07:49:09+00:00</t>
+    <t>2023-04-13T08:12:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T08:12:13+00:00</t>
+    <t>2023-04-13T08:22:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T08:22:34+00:00</t>
+    <t>2023-04-13T08:33:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T08:33:21+00:00</t>
+    <t>2023-04-13T08:34:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T08:34:34+00:00</t>
+    <t>2023-04-13T08:54:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2476,7 +2476,7 @@
         <v>81</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>73</v>
@@ -2584,7 +2584,7 @@
         <v>81</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>73</v>
@@ -2692,7 +2692,7 @@
         <v>81</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>73</v>
@@ -2800,7 +2800,7 @@
         <v>81</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>73</v>
@@ -2908,7 +2908,7 @@
         <v>81</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>73</v>
@@ -3016,7 +3016,7 @@
         <v>81</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>73</v>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T08:54:00+00:00</t>
+    <t>2023-04-13T09:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T09:51:53+00:00</t>
+    <t>2023-04-13T10:21:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T10:21:56+00:00</t>
+    <t>2023-04-13T12:58:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T12:58:26+00:00</t>
+    <t>2023-04-13T15:00:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T15:00:08+00:00</t>
+    <t>2023-04-13T15:16:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T15:16:05+00:00</t>
+    <t>2023-04-14T12:31:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-14T12:31:23+00:00</t>
+    <t>2023-04-14T12:45:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-14T12:45:28+00:00</t>
+    <t>2023-04-14T13:02:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-14T13:02:26+00:00</t>
+    <t>2023-04-14T13:12:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-14T13:12:31+00:00</t>
+    <t>2023-04-17T08:15:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T08:15:24+00:00</t>
+    <t>2023-04-17T08:17:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T08:17:23+00:00</t>
+    <t>2023-04-17T08:37:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T08:37:32+00:00</t>
+    <t>2023-04-17T09:07:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T09:07:20+00:00</t>
+    <t>2023-04-17T10:39:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T10:39:40+00:00</t>
+    <t>2023-04-17T10:56:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T10:56:20+00:00</t>
+    <t>2023-04-17T11:14:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T11:14:19+00:00</t>
+    <t>2023-04-17T11:17:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T11:17:21+00:00</t>
+    <t>2023-04-17T11:39:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T11:39:02+00:00</t>
+    <t>2023-04-17T11:54:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T11:54:58+00:00</t>
+    <t>2023-04-17T12:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T12:02:32+00:00</t>
+    <t>2023-04-17T13:37:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T13:37:35+00:00</t>
+    <t>2023-04-17T14:05:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T14:05:09+00:00</t>
+    <t>2023-04-20T17:39:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-20T17:39:34+00:00</t>
+    <t>2023-04-20T17:42:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-20T17:42:03+00:00</t>
+    <t>2023-04-20T17:43:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$65</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1971" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2242" uniqueCount="398">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-20T17:43:10+00:00</t>
+    <t>2023-04-20T17:43:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -311,13 +311,193 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>HealthcareService.implicitRules</t>
+    <t>HealthcareService.meta.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.versionId</t>
+  </si>
+  <si>
+    <t>Version specific identifier</t>
+  </si>
+  <si>
+    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
+  </si>
+  <si>
+    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
+  </si>
+  <si>
+    <t>Meta.versionId</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.lastUpdated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instant
+</t>
+  </si>
+  <si>
+    <t>When the resource version last changed</t>
+  </si>
+  <si>
+    <t>When the resource last changed - e.g. when the version changed.</t>
+  </si>
+  <si>
+    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
+  </si>
+  <si>
+    <t>Meta.lastUpdated</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.source</t>
   </si>
   <si>
     <t xml:space="preserve">uri
 </t>
   </si>
   <si>
+    <t>Identifies where the resource comes from</t>
+  </si>
+  <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+  </si>
+  <si>
+    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
+This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
+  </si>
+  <si>
+    <t>Meta.source</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(StructureDefinition)
+</t>
+  </si>
+  <si>
+    <t>Profiles this resource claims to conform to</t>
+  </si>
+  <si>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
+  </si>
+  <si>
+    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
+  </si>
+  <si>
+    <t>Meta.profile</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Security Labels applied to this resource</t>
+  </si>
+  <si>
+    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
+  </si>
+  <si>
+    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+  </si>
+  <si>
+    <t>Meta.security</t>
+  </si>
+  <si>
+    <t>CV</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.tag</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
+  </si>
+  <si>
+    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+  </si>
+  <si>
+    <t>Meta.tag</t>
+  </si>
+  <si>
+    <t>HealthcareService.implicitRules</t>
+  </si>
+  <si>
     <t>A set of rules under which this content was created</t>
   </si>
   <si>
@@ -328,9 +508,6 @@
   </si>
   <si>
     <t>Resource.implicitRules</t>
-  </si>
-  <si>
-    <t>n/a</t>
   </si>
   <si>
     <t>HealthcareService.language</t>
@@ -413,31 +590,13 @@
     <t>HealthcareService.extension</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
     <t>Extension</t>
   </si>
   <si>
     <t>An Extension</t>
   </si>
   <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>HealthcareService.extension:activityType</t>
@@ -509,10 +668,6 @@
     <t>HealthcareService.modifierExtension</t>
   </si>
   <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
     <t>Extensions that cannot be ignored</t>
   </si>
   <si>
@@ -520,9 +675,6 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
@@ -696,10 +848,6 @@
     <t>HealthcareService.name</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
     <t>Description of service as presented to a consumer while searching</t>
   </si>
   <si>
@@ -819,9 +967,6 @@
     <t>The provision means being commissioned by, contractually obliged or financially sourced. Types of costings that may apply to this healthcare service, such if the service may be available for free, some discounts available, or fees apply.</t>
   </si>
   <si>
-    <t>example</t>
-  </si>
-  <si>
     <t>http://hl7.org/fhir/ValueSet/service-provision-conditions</t>
   </si>
   <si>
@@ -844,25 +989,7 @@
     <t>HealthcareService.eligibility.id</t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
     <t>HealthcareService.eligibility.extension</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>HealthcareService.eligibility.modifierExtension</t>
@@ -1439,7 +1566,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL57"/>
+  <dimension ref="A1:AL65"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="56.546875" customWidth="true" bestFit="true"/>
@@ -1466,7 +1593,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="87.19921875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="109.73046875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
@@ -1939,10 +2066,10 @@
         <v>73</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K5" t="s" s="2">
         <v>97</v>
@@ -1953,9 +2080,7 @@
       <c r="M5" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="N5" t="s" s="2">
-        <v>100</v>
-      </c>
+      <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
         <v>73</v>
@@ -2004,7 +2129,7 @@
         <v>73</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>74</v>
@@ -2013,13 +2138,13 @@
         <v>81</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AL5" t="s" s="2">
         <v>73</v>
@@ -2027,21 +2152,21 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>73</v>
@@ -2088,28 +2213,28 @@
         <v>73</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y6" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z6" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB6" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="Y6" t="s" s="2">
+      <c r="AC6" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AD6" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE6" t="s" s="2">
         <v>110</v>
-      </c>
-      <c r="AA6" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>73</v>
       </c>
       <c r="AF6" t="s" s="2">
         <v>111</v>
@@ -2118,16 +2243,16 @@
         <v>74</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="AL6" t="s" s="2">
         <v>73</v>
@@ -2135,14 +2260,14 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>113</v>
+        <v>73</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2158,19 +2283,19 @@
         <v>73</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="L7" t="s" s="2">
+      <c r="M7" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="M7" t="s" s="2">
+      <c r="N7" t="s" s="2">
         <v>116</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>117</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2220,7 +2345,7 @@
         <v>73</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>74</v>
@@ -2235,7 +2360,7 @@
         <v>94</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="AL7" t="s" s="2">
         <v>73</v>
@@ -2243,21 +2368,21 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>121</v>
+        <v>73</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>73</v>
@@ -2266,19 +2391,19 @@
         <v>73</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="L8" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="M8" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="N8" t="s" s="2">
         <v>122</v>
-      </c>
-      <c r="L8" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>125</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2328,22 +2453,22 @@
         <v>73</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="AL8" t="s" s="2">
         <v>73</v>
@@ -2351,10 +2476,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2362,11 +2487,11 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G9" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="G9" t="s" s="2">
-        <v>75</v>
-      </c>
       <c r="H9" t="s" s="2">
         <v>73</v>
       </c>
@@ -2374,18 +2499,20 @@
         <v>73</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="M9" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="N9" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L9" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>73</v>
@@ -2422,34 +2549,34 @@
         <v>73</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>131</v>
+        <v>73</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>132</v>
+        <v>73</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>133</v>
+        <v>73</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>135</v>
+        <v>94</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="AL9" t="s" s="2">
         <v>73</v>
@@ -2457,14 +2584,12 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="C10" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
         <v>73</v>
       </c>
@@ -2473,27 +2598,29 @@
         <v>74</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H10" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I10" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J10" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="I10" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J10" t="s" s="2">
-        <v>73</v>
-      </c>
       <c r="K10" t="s" s="2">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="N10" s="2"/>
+        <v>133</v>
+      </c>
+      <c r="N10" t="s" s="2">
+        <v>134</v>
+      </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>73</v>
@@ -2542,7 +2669,7 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
@@ -2554,10 +2681,10 @@
         <v>93</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>135</v>
+        <v>94</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="AL10" t="s" s="2">
         <v>73</v>
@@ -2565,14 +2692,12 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="C11" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
         <v>73</v>
       </c>
@@ -2581,27 +2706,29 @@
         <v>74</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J11" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="I11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J11" t="s" s="2">
-        <v>73</v>
-      </c>
       <c r="K11" t="s" s="2">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="L11" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="M11" t="s" s="2">
         <v>139</v>
       </c>
-      <c r="M11" t="s" s="2">
+      <c r="N11" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="N11" s="2"/>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>73</v>
@@ -2626,13 +2753,13 @@
         <v>73</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>73</v>
+        <v>141</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>73</v>
+        <v>142</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>73</v>
+        <v>143</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>73</v>
@@ -2650,7 +2777,7 @@
         <v>73</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>74</v>
@@ -2662,10 +2789,10 @@
         <v>93</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>135</v>
+        <v>94</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>95</v>
+        <v>145</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>73</v>
@@ -2673,43 +2800,43 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="C12" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
         <v>73</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J12" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="I12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J12" t="s" s="2">
-        <v>73</v>
-      </c>
       <c r="K12" t="s" s="2">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="N12" s="2"/>
+        <v>148</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>73</v>
@@ -2734,13 +2861,13 @@
         <v>73</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>73</v>
+        <v>150</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>73</v>
+        <v>151</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>73</v>
+        <v>152</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>73</v>
@@ -2758,7 +2885,7 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>134</v>
+        <v>153</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
@@ -2770,10 +2897,10 @@
         <v>93</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>135</v>
+        <v>94</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>95</v>
+        <v>145</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>73</v>
@@ -2781,14 +2908,12 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="C13" t="s" s="2">
-        <v>148</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
         <v>73</v>
       </c>
@@ -2800,24 +2925,26 @@
         <v>81</v>
       </c>
       <c r="H13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I13" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="I13" t="s" s="2">
-        <v>73</v>
-      </c>
       <c r="J13" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>149</v>
+        <v>125</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="N13" s="2"/>
+        <v>156</v>
+      </c>
+      <c r="N13" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>73</v>
@@ -2866,22 +2993,22 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>135</v>
+        <v>94</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>73</v>
@@ -2889,14 +3016,12 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="C14" t="s" s="2">
-        <v>151</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
         <v>73</v>
       </c>
@@ -2908,7 +3033,7 @@
         <v>81</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>73</v>
@@ -2917,15 +3042,17 @@
         <v>73</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="N14" s="2"/>
+        <v>162</v>
+      </c>
+      <c r="N14" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>73</v>
@@ -2950,13 +3077,13 @@
         <v>73</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>73</v>
+        <v>164</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>73</v>
+        <v>165</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>73</v>
+        <v>166</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>73</v>
@@ -2974,22 +3101,22 @@
         <v>73</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>134</v>
+        <v>167</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>135</v>
+        <v>94</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>73</v>
@@ -2997,16 +3124,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="C15" t="s" s="2">
-        <v>154</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>73</v>
+        <v>169</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3016,7 +3141,7 @@
         <v>81</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>73</v>
@@ -3025,15 +3150,17 @@
         <v>73</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>139</v>
+        <v>171</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="N15" s="2"/>
+        <v>172</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>173</v>
+      </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>73</v>
@@ -3082,22 +3209,22 @@
         <v>73</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>134</v>
+        <v>174</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>135</v>
+        <v>94</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>95</v>
+        <v>175</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>73</v>
@@ -3105,14 +3232,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>157</v>
+        <v>177</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3125,26 +3252,24 @@
         <v>73</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="J16" t="s" s="2">
         <v>73</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>128</v>
+        <v>178</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>161</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>73</v>
       </c>
@@ -3180,19 +3305,19 @@
         <v>73</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>131</v>
+        <v>73</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>132</v>
+        <v>73</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>133</v>
+        <v>73</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>74</v>
@@ -3201,10 +3326,10 @@
         <v>75</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>135</v>
+        <v>73</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>95</v>
@@ -3215,10 +3340,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3226,7 +3351,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>75</v>
@@ -3238,16 +3363,16 @@
         <v>73</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>164</v>
+        <v>104</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3286,19 +3411,19 @@
         <v>73</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>73</v>
+        <v>109</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>163</v>
+        <v>186</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>74</v>
@@ -3310,23 +3435,25 @@
         <v>93</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>167</v>
+        <v>73</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>168</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="C18" s="2"/>
+        <v>183</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>188</v>
+      </c>
       <c r="D18" t="s" s="2">
         <v>73</v>
       </c>
@@ -3338,33 +3465,29 @@
         <v>81</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>170</v>
+        <v>189</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>171</v>
+        <v>190</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>173</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="Q18" t="s" s="2">
-        <v>174</v>
-      </c>
+      <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
         <v>73</v>
       </c>
@@ -3408,35 +3531,37 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>175</v>
+        <v>95</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>176</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="C19" s="2"/>
+        <v>183</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>193</v>
+      </c>
       <c r="D19" t="s" s="2">
         <v>73</v>
       </c>
@@ -3448,26 +3573,24 @@
         <v>81</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>178</v>
+        <v>194</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>181</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>73</v>
@@ -3516,22 +3639,22 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>182</v>
+        <v>112</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>183</v>
+        <v>95</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>73</v>
@@ -3539,43 +3662,43 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="C20" s="2"/>
+        <v>183</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>196</v>
+      </c>
       <c r="D20" t="s" s="2">
-        <v>185</v>
+        <v>73</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>189</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>73</v>
@@ -3600,13 +3723,13 @@
         <v>73</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>190</v>
+        <v>73</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>191</v>
+        <v>73</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>192</v>
+        <v>73</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>73</v>
@@ -3624,7 +3747,7 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>74</v>
@@ -3636,54 +3759,54 @@
         <v>93</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>193</v>
+        <v>95</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>194</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="C21" s="2"/>
+        <v>183</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="D21" t="s" s="2">
-        <v>196</v>
+        <v>73</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>199</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>73</v>
@@ -3708,13 +3831,13 @@
         <v>73</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>190</v>
+        <v>73</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>200</v>
+        <v>73</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>201</v>
+        <v>73</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>73</v>
@@ -3732,7 +3855,7 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>74</v>
@@ -3744,10 +3867,10 @@
         <v>93</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>202</v>
+        <v>95</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>73</v>
@@ -3755,12 +3878,14 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="C22" s="2"/>
+        <v>183</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>202</v>
+      </c>
       <c r="D22" t="s" s="2">
         <v>73</v>
       </c>
@@ -3769,7 +3894,7 @@
         <v>74</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>82</v>
@@ -3778,20 +3903,18 @@
         <v>73</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>199</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>73</v>
@@ -3816,13 +3939,13 @@
         <v>73</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>206</v>
+        <v>73</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>207</v>
+        <v>73</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>73</v>
@@ -3840,7 +3963,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>203</v>
+        <v>186</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>74</v>
@@ -3852,10 +3975,10 @@
         <v>93</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>202</v>
+        <v>95</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>73</v>
@@ -3863,12 +3986,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="C23" s="2"/>
+        <v>183</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>205</v>
+      </c>
       <c r="D23" t="s" s="2">
         <v>73</v>
       </c>
@@ -3877,7 +4002,7 @@
         <v>74</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>82</v>
@@ -3886,20 +4011,18 @@
         <v>73</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>212</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>73</v>
@@ -3948,7 +4071,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>208</v>
+        <v>186</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
@@ -3960,55 +4083,57 @@
         <v>93</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>182</v>
+        <v>112</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>213</v>
+        <v>95</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>214</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I24" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="I24" t="s" s="2">
-        <v>73</v>
-      </c>
       <c r="J24" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>216</v>
+        <v>104</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="O24" s="2"/>
+        <v>107</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>210</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>73</v>
       </c>
@@ -4044,34 +4169,34 @@
         <v>73</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>73</v>
+        <v>109</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>220</v>
+        <v>95</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>73</v>
@@ -4079,10 +4204,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4093,10 +4218,10 @@
         <v>74</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>73</v>
@@ -4105,17 +4230,15 @@
         <v>82</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>224</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>73</v>
@@ -4164,13 +4287,13 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>93</v>
@@ -4179,18 +4302,18 @@
         <v>94</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>73</v>
+        <v>217</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4204,31 +4327,33 @@
         <v>81</v>
       </c>
       <c r="H26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I26" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="I26" t="s" s="2">
-        <v>73</v>
-      </c>
       <c r="J26" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="Q26" s="2"/>
+      <c r="Q26" t="s" s="2">
+        <v>223</v>
+      </c>
       <c r="R26" t="s" s="2">
         <v>73</v>
       </c>
@@ -4272,7 +4397,7 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>74</v>
@@ -4287,18 +4412,18 @@
         <v>94</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>73</v>
+        <v>225</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4312,7 +4437,7 @@
         <v>81</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>73</v>
@@ -4321,16 +4446,16 @@
         <v>82</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4380,7 +4505,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>
@@ -4392,10 +4517,10 @@
         <v>93</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>73</v>
@@ -4403,14 +4528,14 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>73</v>
+        <v>234</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4420,25 +4545,25 @@
         <v>75</v>
       </c>
       <c r="H28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J28" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="I28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J28" t="s" s="2">
-        <v>73</v>
-      </c>
       <c r="K28" t="s" s="2">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4464,13 +4589,13 @@
         <v>73</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>73</v>
+        <v>239</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>73</v>
+        <v>240</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>73</v>
+        <v>241</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>73</v>
@@ -4488,7 +4613,7 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
@@ -4500,25 +4625,25 @@
         <v>93</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>244</v>
+        <v>94</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>73</v>
+        <v>243</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>73</v>
+        <v>245</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -4528,25 +4653,25 @@
         <v>75</v>
       </c>
       <c r="H29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J29" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="I29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J29" t="s" s="2">
-        <v>73</v>
-      </c>
       <c r="K29" t="s" s="2">
-        <v>209</v>
+        <v>235</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4572,13 +4697,13 @@
         <v>73</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>73</v>
+        <v>239</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>73</v>
+        <v>249</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>73</v>
+        <v>250</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>73</v>
@@ -4596,7 +4721,7 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
@@ -4608,10 +4733,10 @@
         <v>93</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>182</v>
+        <v>94</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>73</v>
@@ -4619,10 +4744,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4642,19 +4767,19 @@
         <v>73</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>186</v>
+        <v>235</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4680,10 +4805,10 @@
         <v>73</v>
       </c>
       <c r="X30" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="Y30" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="Y30" t="s" s="2">
-        <v>253</v>
       </c>
       <c r="Z30" t="s" s="2">
         <v>256</v>
@@ -4704,7 +4829,7 @@
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
@@ -4719,7 +4844,7 @@
         <v>94</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>73</v>
@@ -4727,10 +4852,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4750,18 +4875,20 @@
         <v>73</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>73</v>
@@ -4810,7 +4937,7 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
@@ -4822,21 +4949,21 @@
         <v>93</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>94</v>
+        <v>231</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>102</v>
+        <v>262</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>73</v>
+        <v>263</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4850,24 +4977,26 @@
         <v>81</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>216</v>
+        <v>97</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>266</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>73</v>
@@ -4916,7 +5045,7 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>74</v>
@@ -4925,13 +5054,13 @@
         <v>81</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>102</v>
+        <v>268</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>73</v>
@@ -4939,42 +5068,42 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>157</v>
+        <v>73</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>128</v>
+        <v>97</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>160</v>
+        <v>272</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5012,16 +5141,16 @@
         <v>73</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>131</v>
+        <v>73</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>132</v>
+        <v>73</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>133</v>
+        <v>73</v>
       </c>
       <c r="AF33" t="s" s="2">
         <v>269</v>
@@ -5030,16 +5159,16 @@
         <v>74</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>135</v>
+        <v>94</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>95</v>
+        <v>273</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>73</v>
@@ -5047,46 +5176,44 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>271</v>
+        <v>73</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>128</v>
+        <v>275</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>161</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>73</v>
       </c>
@@ -5140,16 +5267,16 @@
         <v>74</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>135</v>
+        <v>94</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>95</v>
+        <v>279</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>73</v>
@@ -5157,10 +5284,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5174,25 +5301,25 @@
         <v>81</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>186</v>
+        <v>281</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>199</v>
+        <v>284</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5218,10 +5345,10 @@
         <v>73</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>255</v>
+        <v>73</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>278</v>
+        <v>73</v>
       </c>
       <c r="Z35" t="s" s="2">
         <v>73</v>
@@ -5242,7 +5369,7 @@
         <v>73</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>74</v>
@@ -5254,10 +5381,10 @@
         <v>93</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>94</v>
+        <v>285</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>257</v>
+        <v>286</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>73</v>
@@ -5265,10 +5392,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5279,10 +5406,10 @@
         <v>74</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>73</v>
@@ -5291,16 +5418,16 @@
         <v>73</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>227</v>
+        <v>288</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5350,22 +5477,22 @@
         <v>73</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>94</v>
+        <v>292</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>73</v>
@@ -5373,10 +5500,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5399,16 +5526,16 @@
         <v>73</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>186</v>
+        <v>258</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5434,13 +5561,13 @@
         <v>73</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>255</v>
+        <v>73</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>288</v>
+        <v>73</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>289</v>
+        <v>73</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>73</v>
@@ -5458,7 +5585,7 @@
         <v>73</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>74</v>
@@ -5470,10 +5597,10 @@
         <v>93</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>94</v>
+        <v>231</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>73</v>
@@ -5481,10 +5608,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5498,7 +5625,7 @@
         <v>75</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>73</v>
@@ -5507,16 +5634,16 @@
         <v>73</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>186</v>
+        <v>235</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5542,13 +5669,13 @@
         <v>73</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>73</v>
@@ -5566,7 +5693,7 @@
         <v>73</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>74</v>
@@ -5581,7 +5708,7 @@
         <v>94</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>290</v>
+        <v>304</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>73</v>
@@ -5589,10 +5716,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5615,17 +5742,15 @@
         <v>73</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>186</v>
+        <v>306</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>300</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>73</v>
@@ -5650,13 +5775,13 @@
         <v>73</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>109</v>
+        <v>73</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>73</v>
@@ -5674,7 +5799,7 @@
         <v>73</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>74</v>
@@ -5689,7 +5814,7 @@
         <v>94</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>301</v>
+        <v>101</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>73</v>
@@ -5697,10 +5822,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5711,10 +5836,10 @@
         <v>74</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>73</v>
@@ -5723,17 +5848,15 @@
         <v>73</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>186</v>
+        <v>97</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>303</v>
+        <v>98</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>199</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>73</v>
@@ -5758,13 +5881,13 @@
         <v>73</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>255</v>
+        <v>73</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>305</v>
+        <v>73</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>306</v>
+        <v>73</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>73</v>
@@ -5782,22 +5905,22 @@
         <v>73</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>302</v>
+        <v>100</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>290</v>
+        <v>101</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>73</v>
@@ -5805,24 +5928,24 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>73</v>
@@ -5831,15 +5954,17 @@
         <v>73</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>170</v>
+        <v>104</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>308</v>
+        <v>105</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>106</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>73</v>
@@ -5876,34 +6001,34 @@
         <v>73</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>73</v>
+        <v>109</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>307</v>
+        <v>111</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>290</v>
+        <v>95</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>73</v>
@@ -5911,14 +6036,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>73</v>
+        <v>312</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -5928,27 +6053,29 @@
         <v>75</v>
       </c>
       <c r="H42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I42" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="I42" t="s" s="2">
-        <v>73</v>
-      </c>
       <c r="J42" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>259</v>
+        <v>104</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="O42" s="2"/>
+        <v>107</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>210</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>73</v>
       </c>
@@ -5996,7 +6123,7 @@
         <v>73</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>74</v>
@@ -6008,10 +6135,10 @@
         <v>93</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>314</v>
+        <v>95</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>73</v>
@@ -6019,10 +6146,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6045,15 +6172,17 @@
         <v>73</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>216</v>
+        <v>235</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>263</v>
+        <v>317</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>318</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>248</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>73</v>
@@ -6078,10 +6207,10 @@
         <v>73</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>73</v>
+        <v>150</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>73</v>
+        <v>319</v>
       </c>
       <c r="Z43" t="s" s="2">
         <v>73</v>
@@ -6102,7 +6231,7 @@
         <v>73</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>265</v>
+        <v>316</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>74</v>
@@ -6111,13 +6240,13 @@
         <v>81</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>102</v>
+        <v>304</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>73</v>
@@ -6125,21 +6254,21 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>157</v>
+        <v>73</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>73</v>
@@ -6151,16 +6280,16 @@
         <v>73</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>128</v>
+        <v>275</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>267</v>
+        <v>321</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>268</v>
+        <v>322</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>160</v>
+        <v>323</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6198,34 +6327,34 @@
         <v>73</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>131</v>
+        <v>73</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>132</v>
+        <v>73</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>133</v>
+        <v>73</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>269</v>
+        <v>320</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>135</v>
+        <v>94</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>95</v>
+        <v>324</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>73</v>
@@ -6233,14 +6362,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>271</v>
+        <v>73</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6250,29 +6379,27 @@
         <v>75</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>128</v>
+        <v>235</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>272</v>
+        <v>326</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>273</v>
+        <v>327</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>161</v>
-      </c>
+        <v>328</v>
+      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>73</v>
       </c>
@@ -6296,13 +6423,13 @@
         <v>73</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>73</v>
+        <v>150</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>73</v>
+        <v>329</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>73</v>
+        <v>330</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>73</v>
@@ -6320,7 +6447,7 @@
         <v>73</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>274</v>
+        <v>325</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>74</v>
@@ -6332,10 +6459,10 @@
         <v>93</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>135</v>
+        <v>94</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>95</v>
+        <v>331</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>73</v>
@@ -6343,10 +6470,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6369,16 +6496,16 @@
         <v>73</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>104</v>
+        <v>235</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>219</v>
+        <v>335</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6404,13 +6531,13 @@
         <v>73</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>190</v>
+        <v>239</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>321</v>
+        <v>336</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>322</v>
+        <v>337</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>73</v>
@@ -6428,7 +6555,7 @@
         <v>73</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>74</v>
@@ -6443,7 +6570,7 @@
         <v>94</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>314</v>
+        <v>331</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>73</v>
@@ -6451,10 +6578,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6465,10 +6592,10 @@
         <v>74</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>73</v>
@@ -6477,15 +6604,17 @@
         <v>73</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>170</v>
+        <v>235</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>324</v>
+        <v>339</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>340</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>341</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>73</v>
@@ -6510,13 +6639,13 @@
         <v>73</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>73</v>
+        <v>164</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>73</v>
+        <v>165</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>73</v>
+        <v>166</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>73</v>
@@ -6534,13 +6663,13 @@
         <v>73</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>93</v>
@@ -6549,7 +6678,7 @@
         <v>94</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>314</v>
+        <v>342</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>73</v>
@@ -6557,10 +6686,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>326</v>
+        <v>343</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>326</v>
+        <v>343</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6571,10 +6700,10 @@
         <v>74</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>73</v>
@@ -6583,16 +6712,16 @@
         <v>73</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>327</v>
+        <v>235</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>328</v>
+        <v>344</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>329</v>
+        <v>345</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>330</v>
+        <v>248</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6618,13 +6747,13 @@
         <v>73</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>73</v>
+        <v>150</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>73</v>
+        <v>346</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>73</v>
+        <v>347</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>73</v>
@@ -6642,13 +6771,13 @@
         <v>73</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>326</v>
+        <v>343</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>93</v>
@@ -6657,7 +6786,7 @@
         <v>94</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>314</v>
+        <v>331</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>73</v>
@@ -6665,10 +6794,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>331</v>
+        <v>348</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>331</v>
+        <v>348</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6682,7 +6811,7 @@
         <v>81</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>73</v>
@@ -6691,17 +6820,15 @@
         <v>73</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>327</v>
+        <v>219</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>332</v>
+        <v>349</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>350</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>73</v>
@@ -6750,7 +6877,7 @@
         <v>73</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>331</v>
+        <v>348</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>74</v>
@@ -6765,7 +6892,7 @@
         <v>94</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>314</v>
+        <v>331</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>73</v>
@@ -6773,10 +6900,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>334</v>
+        <v>351</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>334</v>
+        <v>351</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6799,15 +6926,17 @@
         <v>73</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>259</v>
+        <v>306</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>335</v>
+        <v>352</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>353</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>354</v>
+      </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>73</v>
@@ -6856,7 +6985,7 @@
         <v>73</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>334</v>
+        <v>351</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>74</v>
@@ -6871,7 +7000,7 @@
         <v>94</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>314</v>
+        <v>355</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>73</v>
@@ -6879,10 +7008,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>337</v>
+        <v>356</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>337</v>
+        <v>356</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6905,13 +7034,13 @@
         <v>73</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>216</v>
+        <v>97</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>263</v>
+        <v>98</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>264</v>
+        <v>99</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6962,7 +7091,7 @@
         <v>73</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>265</v>
+        <v>100</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>74</v>
@@ -6977,7 +7106,7 @@
         <v>73</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>73</v>
@@ -6985,14 +7114,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>338</v>
+        <v>357</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>338</v>
+        <v>357</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>157</v>
+        <v>103</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7011,16 +7140,16 @@
         <v>73</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>267</v>
+        <v>105</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>268</v>
+        <v>106</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>160</v>
+        <v>107</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7058,19 +7187,19 @@
         <v>73</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>133</v>
+        <v>110</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>269</v>
+        <v>111</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>74</v>
@@ -7082,7 +7211,7 @@
         <v>93</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>95</v>
@@ -7093,14 +7222,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>339</v>
+        <v>358</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>339</v>
+        <v>358</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>271</v>
+        <v>312</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -7119,19 +7248,19 @@
         <v>82</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>272</v>
+        <v>313</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>273</v>
+        <v>314</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>160</v>
+        <v>107</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>161</v>
+        <v>210</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>73</v>
@@ -7180,7 +7309,7 @@
         <v>73</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>274</v>
+        <v>315</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>74</v>
@@ -7192,7 +7321,7 @@
         <v>93</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>95</v>
@@ -7203,10 +7332,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>340</v>
+        <v>359</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>340</v>
+        <v>359</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7214,10 +7343,10 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>73</v>
@@ -7229,16 +7358,16 @@
         <v>73</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>216</v>
+        <v>160</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>341</v>
+        <v>360</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>342</v>
+        <v>361</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>219</v>
+        <v>267</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7264,13 +7393,13 @@
         <v>73</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>73</v>
+        <v>239</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>73</v>
+        <v>362</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>73</v>
+        <v>363</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>73</v>
@@ -7288,13 +7417,13 @@
         <v>73</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>340</v>
+        <v>359</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>93</v>
@@ -7303,7 +7432,7 @@
         <v>94</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>102</v>
+        <v>355</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>73</v>
@@ -7311,10 +7440,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>343</v>
+        <v>364</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>343</v>
+        <v>364</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7337,17 +7466,15 @@
         <v>73</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>344</v>
+        <v>219</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>345</v>
+        <v>365</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>347</v>
-      </c>
+        <v>366</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>73</v>
@@ -7396,7 +7523,7 @@
         <v>73</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>343</v>
+        <v>364</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>74</v>
@@ -7408,10 +7535,10 @@
         <v>93</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>348</v>
+        <v>94</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>314</v>
+        <v>355</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>73</v>
@@ -7419,10 +7546,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>349</v>
+        <v>367</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>349</v>
+        <v>367</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7436,7 +7563,7 @@
         <v>81</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>73</v>
@@ -7445,16 +7572,16 @@
         <v>73</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>216</v>
+        <v>368</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>350</v>
+        <v>369</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>351</v>
+        <v>370</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>219</v>
+        <v>371</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -7504,7 +7631,7 @@
         <v>73</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>349</v>
+        <v>367</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>74</v>
@@ -7519,7 +7646,7 @@
         <v>94</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>314</v>
+        <v>355</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>73</v>
@@ -7527,10 +7654,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>352</v>
+        <v>372</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>352</v>
+        <v>372</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7541,10 +7668,10 @@
         <v>74</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>73</v>
@@ -7553,16 +7680,16 @@
         <v>73</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>353</v>
+        <v>368</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>354</v>
+        <v>373</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>355</v>
+        <v>374</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>212</v>
+        <v>371</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -7612,29 +7739,891 @@
         <v>73</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>352</v>
+        <v>372</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>182</v>
+        <v>94</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AL57" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="58" hidden="true">
+      <c r="A58" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
+      <c r="P58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="59" hidden="true">
+      <c r="A59" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
+      <c r="P59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="60" hidden="true">
+      <c r="A60" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="O60" s="2"/>
+      <c r="P60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="61" hidden="true">
+      <c r="A61" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="P61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="62" hidden="true">
+      <c r="A62" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="O62" s="2"/>
+      <c r="P62" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="63" hidden="true">
+      <c r="A63" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="O63" s="2"/>
+      <c r="P63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="AL65" t="s" s="2">
         <v>73</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AL57">
+  <autoFilter ref="A1:AL65">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -7644,7 +8633,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI56">
+  <conditionalFormatting sqref="A2:AI64">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-20T17:43:52+00:00</t>
+    <t>2023-04-28T11:09:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T11:09:12+00:00</t>
+    <t>2023-04-28T15:03:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T15:03:41+00:00</t>
+    <t>2023-04-28T18:35:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T18:35:22+00:00</t>
+    <t>2023-04-28T18:37:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T18:37:07+00:00</t>
+    <t>2023-04-28T18:58:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T18:58:16+00:00</t>
+    <t>2023-05-02T06:31:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T06:31:09+00:00</t>
+    <t>2023-05-02T06:34:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T06:34:44+00:00</t>
+    <t>2023-05-02T07:22:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$57</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2242" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1972" uniqueCount="359">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T07:22:02+00:00</t>
+    <t>2023-05-02T14:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -311,543 +311,401 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>HealthcareService.meta.id</t>
+    <t>HealthcareService.implicitRules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uri
+</t>
+  </si>
+  <si>
+    <t>A set of rules under which this content was created</t>
+  </si>
+  <si>
+    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+  </si>
+  <si>
+    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+  </si>
+  <si>
+    <t>Resource.implicitRules</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>HealthcareService.language</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code
+</t>
+  </si>
+  <si>
+    <t>Language of the resource content</t>
+  </si>
+  <si>
+    <t>The base language in which the resource is written.</t>
+  </si>
+  <si>
+    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
+  </si>
+  <si>
+    <t>preferred</t>
+  </si>
+  <si>
+    <t>A human language.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
+  </si>
+  <si>
+    <t>Resource.language</t>
+  </si>
+  <si>
+    <t>HealthcareService.text</t>
+  </si>
+  <si>
+    <t>narrative
+htmlxhtmldisplay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narrative
+</t>
+  </si>
+  <si>
+    <t>Text summary of the resource, for human interpretation</t>
+  </si>
+  <si>
+    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
+  </si>
+  <si>
+    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+  </si>
+  <si>
+    <t>DomainResource.text</t>
+  </si>
+  <si>
+    <t>Act.text?</t>
+  </si>
+  <si>
+    <t>HealthcareService.contained</t>
+  </si>
+  <si>
+    <t>inline resources
+anonymous resourcescontained resources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resource
+</t>
+  </si>
+  <si>
+    <t>Contained, inline Resources</t>
+  </si>
+  <si>
+    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
+  </si>
+  <si>
+    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+  </si>
+  <si>
+    <t>DomainResource.contained</t>
+  </si>
+  <si>
+    <t>HealthcareService.extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>HealthcareService.extension:activityType</t>
+  </si>
+  <si>
+    <t>activityType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/HealthcareService-activityType}
+</t>
+  </si>
+  <si>
+    <t>Optional Extensions Element</t>
+  </si>
+  <si>
+    <t>Optional Extension Element - found in all resources.</t>
+  </si>
+  <si>
+    <t>HealthcareService.extension:authorizationDate</t>
+  </si>
+  <si>
+    <t>authorizationDate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/HealthcareService-authorizationDate}
+</t>
+  </si>
+  <si>
+    <t>HealthcareService.extension:authorizationNumberARHGOS</t>
+  </si>
+  <si>
+    <t>authorizationNumberARHGOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/HealthcareService-authorizationNumberARHGOS}
+</t>
+  </si>
+  <si>
+    <t>HealthcareService.extension:implementationPeriod</t>
+  </si>
+  <si>
+    <t>implementationPeriod</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/HealthcareService-implementationPeriod}
+</t>
+  </si>
+  <si>
+    <t>HealthcareService.extension:deleteAutorisationImplantation</t>
+  </si>
+  <si>
+    <t>deleteAutorisationImplantation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/HealthcareService-deleteAutorisationImplantation}
+</t>
+  </si>
+  <si>
+    <t>HealthcareService.extension:dateUpdateActivity</t>
+  </si>
+  <si>
+    <t>dateUpdateActivity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/HealthcareService-dateUpdateActivity}
+</t>
+  </si>
+  <si>
+    <t>HealthcareService.modifierExtension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+  </si>
+  <si>
+    <t>DomainResource.modifierExtension</t>
+  </si>
+  <si>
+    <t>HealthcareService.identifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier
+</t>
+  </si>
+  <si>
+    <t>numeroAutorisationARHGOS</t>
+  </si>
+  <si>
+    <t>External identifiers for this item.</t>
+  </si>
+  <si>
+    <t>Identifiant fonctionnel, numéro d'autorisation ARHGOS</t>
+  </si>
+  <si>
+    <t>.id</t>
+  </si>
+  <si>
+    <t>FiveWs.identifier</t>
+  </si>
+  <si>
+    <t>HealthcareService.active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>Whether this HealthcareService record is in active use</t>
+  </si>
+  <si>
+    <t>This flag is used to mark the record to not be used. This is not used when a center is closed for maintenance, or for holidays, the notAvailable period is to be used for this.</t>
+  </si>
+  <si>
+    <t>This element is labeled as a modifier because it may be used to mark that the resource was created in error.</t>
+  </si>
+  <si>
+    <t>This resource is generally assumed to be active if no value is provided for the active element</t>
+  </si>
+  <si>
+    <t>.statusCode</t>
+  </si>
+  <si>
+    <t>FiveWs.status</t>
+  </si>
+  <si>
+    <t>HealthcareService.providedBy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://interopsante.org/fhir/StructureDefinition/FrOrganization|http://interop.esante.gouv.fr/ig/fhir/annuaire-donnee-publique/StructureDefinition/as-organization)
+</t>
+  </si>
+  <si>
+    <t>idStructure</t>
+  </si>
+  <si>
+    <t>The organization that provides this healthcare service.</t>
+  </si>
+  <si>
+    <t>Reference vers l'id de la ressource de la structure FINESS ET à laquelle est rattaché cette activité sanitaire</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
+  </si>
+  <si>
+    <t>.scopingRole.Organization</t>
+  </si>
+  <si>
+    <t>HealthcareService.category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">service category
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>modalite</t>
+  </si>
+  <si>
+    <t>Identifies the broad category of service being performed or delivered.</t>
+  </si>
+  <si>
+    <t>Les modalités sont des modes d’application ou des types de soins prévus par les textes réglementaires encadrant chaque activité de soins</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>Modalité de l'activité de soins</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J132-ModaliteActivite-RASS/FHIR/JDV-J132-ModaliteActivite-RASS</t>
+  </si>
+  <si>
+    <t>.code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>HealthcareService.type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">service type
+</t>
+  </si>
+  <si>
+    <t>Type of service that may be delivered or performed</t>
+  </si>
+  <si>
+    <t>The specific type of service that may be delivered or performed.</t>
+  </si>
+  <si>
+    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
+  </si>
+  <si>
+    <t>Code définissant l'activité de soins autorisée</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J133-ActiviteSanitaireRegulee-RASS/FHIR/JDV-J133-ActiviteSanitaireRegulee-RASS</t>
+  </si>
+  <si>
+    <t>.actrelationship[typeCode=COMP.act[classCode=ACT][moodCode=DEF].code</t>
+  </si>
+  <si>
+    <t>HealthcareService.specialty</t>
+  </si>
+  <si>
+    <t>activite</t>
+  </si>
+  <si>
+    <t>Collection of specialties handled by the service site. This is more of a medical term.</t>
+  </si>
+  <si>
+    <t>Code définissant l'activité de soins autorisée -AS- (article L.6122-1 du CSP), la liste des activités de soins soumises à autorisation est fixée par décret en Conseil d'Etat (article L.6122-25 du CSP)</t>
+  </si>
+  <si>
+    <t>A specialty that a healthcare service may provide.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/c80-practice-codes</t>
+  </si>
+  <si>
+    <t>HealthcareService.location</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Location)
+</t>
+  </si>
+  <si>
+    <t>Location(s) where service may be provided</t>
+  </si>
+  <si>
+    <t>The location(s) where this healthcare service may be provided.</t>
+  </si>
+  <si>
+    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
+  </si>
+  <si>
+    <t>.location.role[classCode=SDLOC]</t>
+  </si>
+  <si>
+    <t>FiveWs.where[x]</t>
+  </si>
+  <si>
+    <t>HealthcareService.name</t>
   </si>
   <si>
     <t xml:space="preserve">string
 </t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>HealthcareService.meta.extension</t>
-  </si>
-  <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>HealthcareService.meta.versionId</t>
-  </si>
-  <si>
-    <t>Version specific identifier</t>
-  </si>
-  <si>
-    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
-  </si>
-  <si>
-    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
-  </si>
-  <si>
-    <t>Meta.versionId</t>
-  </si>
-  <si>
-    <t>HealthcareService.meta.lastUpdated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">instant
-</t>
-  </si>
-  <si>
-    <t>When the resource version last changed</t>
-  </si>
-  <si>
-    <t>When the resource last changed - e.g. when the version changed.</t>
-  </si>
-  <si>
-    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
-  </si>
-  <si>
-    <t>Meta.lastUpdated</t>
-  </si>
-  <si>
-    <t>HealthcareService.meta.source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">uri
-</t>
-  </si>
-  <si>
-    <t>Identifies where the resource comes from</t>
-  </si>
-  <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
-  </si>
-  <si>
-    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
-This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
-  </si>
-  <si>
-    <t>Meta.source</t>
-  </si>
-  <si>
-    <t>HealthcareService.meta.profile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
-</t>
-  </si>
-  <si>
-    <t>Profiles this resource claims to conform to</t>
-  </si>
-  <si>
-    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
-  </si>
-  <si>
-    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
-  </si>
-  <si>
-    <t>Meta.profile</t>
-  </si>
-  <si>
-    <t>HealthcareService.meta.security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Security Labels applied to this resource</t>
-  </si>
-  <si>
-    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
-  </si>
-  <si>
-    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
-  </si>
-  <si>
-    <t>Meta.security</t>
-  </si>
-  <si>
-    <t>CV</t>
-  </si>
-  <si>
-    <t>HealthcareService.meta.tag</t>
-  </si>
-  <si>
-    <t>Tags applied to this resource</t>
-  </si>
-  <si>
-    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
-  </si>
-  <si>
-    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
-  </si>
-  <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
-  </si>
-  <si>
-    <t>Meta.tag</t>
-  </si>
-  <si>
-    <t>HealthcareService.implicitRules</t>
-  </si>
-  <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
-  </si>
-  <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
-  </si>
-  <si>
-    <t>Resource.implicitRules</t>
-  </si>
-  <si>
-    <t>HealthcareService.language</t>
-  </si>
-  <si>
-    <t xml:space="preserve">code
-</t>
-  </si>
-  <si>
-    <t>Language of the resource content</t>
-  </si>
-  <si>
-    <t>The base language in which the resource is written.</t>
-  </si>
-  <si>
-    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
-  </si>
-  <si>
-    <t>preferred</t>
-  </si>
-  <si>
-    <t>A human language.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
-  </si>
-  <si>
-    <t>Resource.language</t>
-  </si>
-  <si>
-    <t>HealthcareService.text</t>
-  </si>
-  <si>
-    <t>narrative
-htmlxhtmldisplay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narrative
-</t>
-  </si>
-  <si>
-    <t>Text summary of the resource, for human interpretation</t>
-  </si>
-  <si>
-    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
-  </si>
-  <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
-  </si>
-  <si>
-    <t>DomainResource.text</t>
-  </si>
-  <si>
-    <t>Act.text?</t>
-  </si>
-  <si>
-    <t>HealthcareService.contained</t>
-  </si>
-  <si>
-    <t>inline resources
-anonymous resourcescontained resources</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resource
-</t>
-  </si>
-  <si>
-    <t>Contained, inline Resources</t>
-  </si>
-  <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
-  </si>
-  <si>
-    <t>DomainResource.contained</t>
-  </si>
-  <si>
-    <t>HealthcareService.extension</t>
-  </si>
-  <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>HealthcareService.extension:activityType</t>
-  </si>
-  <si>
-    <t>activityType</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/HealthcareService-activityType}
-</t>
-  </si>
-  <si>
-    <t>Optional Extensions Element</t>
-  </si>
-  <si>
-    <t>Optional Extension Element - found in all resources.</t>
-  </si>
-  <si>
-    <t>HealthcareService.extension:authorizationDate</t>
-  </si>
-  <si>
-    <t>authorizationDate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/HealthcareService-authorizationDate}
-</t>
-  </si>
-  <si>
-    <t>HealthcareService.extension:authorizationNumberARHGOS</t>
-  </si>
-  <si>
-    <t>authorizationNumberARHGOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/HealthcareService-authorizationNumberARHGOS}
-</t>
-  </si>
-  <si>
-    <t>HealthcareService.extension:implementationPeriod</t>
-  </si>
-  <si>
-    <t>implementationPeriod</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/HealthcareService-implementationPeriod}
-</t>
-  </si>
-  <si>
-    <t>HealthcareService.extension:deleteAutorisationImplantation</t>
-  </si>
-  <si>
-    <t>deleteAutorisationImplantation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/HealthcareService-deleteAutorisationImplantation}
-</t>
-  </si>
-  <si>
-    <t>HealthcareService.extension:dateUpdateActivity</t>
-  </si>
-  <si>
-    <t>dateUpdateActivity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/HealthcareService-dateUpdateActivity}
-</t>
-  </si>
-  <si>
-    <t>HealthcareService.modifierExtension</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
-  </si>
-  <si>
-    <t>DomainResource.modifierExtension</t>
-  </si>
-  <si>
-    <t>HealthcareService.identifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifier
-</t>
-  </si>
-  <si>
-    <t>Numéro autorisation ARGHOS</t>
-  </si>
-  <si>
-    <t>External identifiers for this item.</t>
-  </si>
-  <si>
-    <t>.id</t>
-  </si>
-  <si>
-    <t>FiveWs.identifier</t>
-  </si>
-  <si>
-    <t>HealthcareService.active</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>Whether this HealthcareService record is in active use</t>
-  </si>
-  <si>
-    <t>This flag is used to mark the record to not be used. This is not used when a center is closed for maintenance, or for holidays, the notAvailable period is to be used for this.</t>
-  </si>
-  <si>
-    <t>This element is labeled as a modifier because it may be used to mark that the resource was created in error.</t>
-  </si>
-  <si>
-    <t>This resource is generally assumed to be active if no value is provided for the active element</t>
-  </si>
-  <si>
-    <t>.statusCode</t>
-  </si>
-  <si>
-    <t>FiveWs.status</t>
-  </si>
-  <si>
-    <t>HealthcareService.providedBy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Organization)
-</t>
-  </si>
-  <si>
-    <t>Référence vers la structure FINESS ET</t>
-  </si>
-  <si>
-    <t>The organization that provides this healthcare service.</t>
-  </si>
-  <si>
-    <t>Reference vers l'id de la ressource de la structure FINESS ET à laquelle est rattaché cette activité sanitaire</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
-  </si>
-  <si>
-    <t>.scopingRole.Organization</t>
-  </si>
-  <si>
-    <t>HealthcareService.category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">service category
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
-    <t>Broad category of service being performed or delivered</t>
-  </si>
-  <si>
-    <t>Identifies the broad category of service being performed or delivered.</t>
-  </si>
-  <si>
-    <t>Selecting a Service Category then determines the list of relevant service types that can be selected in the primary service type.</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>Modalité de l'activité de soins</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J132-ModaliteActivite-RASS/FHIR/JDV-J132-ModaliteActivite-RASS</t>
-  </si>
-  <si>
-    <t>.code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>HealthcareService.type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">service type
-</t>
-  </si>
-  <si>
-    <t>Type of service that may be delivered or performed</t>
-  </si>
-  <si>
-    <t>The specific type of service that may be delivered or performed.</t>
-  </si>
-  <si>
-    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
-  </si>
-  <si>
-    <t>Code définissant l'activité de soins autorisée</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J133-ActiviteSanitaireRegulee-RASS/FHIR/JDV-J133-ActiviteSanitaireRegulee-RASS</t>
-  </si>
-  <si>
-    <t>.actrelationship[typeCode=COMP.act[classCode=ACT][moodCode=DEF].code</t>
-  </si>
-  <si>
-    <t>HealthcareService.specialty</t>
-  </si>
-  <si>
-    <t>Specialties handled by the HealthcareService</t>
-  </si>
-  <si>
-    <t>Collection of specialties handled by the service site. This is more of a medical term.</t>
-  </si>
-  <si>
-    <t>A specialty that a healthcare service may provide.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/c80-practice-codes</t>
-  </si>
-  <si>
-    <t>HealthcareService.location</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Location)
-</t>
-  </si>
-  <si>
-    <t>Location(s) where service may be provided</t>
-  </si>
-  <si>
-    <t>The location(s) where this healthcare service may be provided.</t>
-  </si>
-  <si>
-    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
-  </si>
-  <si>
-    <t>.location.role[classCode=SDLOC]</t>
-  </si>
-  <si>
-    <t>FiveWs.where[x]</t>
-  </si>
-  <si>
-    <t>HealthcareService.name</t>
-  </si>
-  <si>
     <t>Description of service as presented to a consumer while searching</t>
   </si>
   <si>
@@ -967,6 +825,9 @@
     <t>The provision means being commissioned by, contractually obliged or financially sourced. Types of costings that may apply to this healthcare service, such if the service may be available for free, some discounts available, or fees apply.</t>
   </si>
   <si>
+    <t>example</t>
+  </si>
+  <si>
     <t>http://hl7.org/fhir/ValueSet/service-provision-conditions</t>
   </si>
   <si>
@@ -989,7 +850,25 @@
     <t>HealthcareService.eligibility.id</t>
   </si>
   <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
     <t>HealthcareService.eligibility.extension</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
   </si>
   <si>
     <t>HealthcareService.eligibility.modifierExtension</t>
@@ -1060,7 +939,7 @@
     <t>HealthcareService.characteristic</t>
   </si>
   <si>
-    <t>Collection of characteristics (attributes)</t>
+    <t>forme</t>
   </si>
   <si>
     <t>Collection of characteristics (attributes).</t>
@@ -1566,7 +1445,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL65"/>
+  <dimension ref="A1:AL57"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="56.546875" customWidth="true" bestFit="true"/>
@@ -1579,7 +1458,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="122.28515625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="159.0546875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1593,7 +1472,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="87.19921875" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="109.73046875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
@@ -2066,10 +1945,10 @@
         <v>73</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K5" t="s" s="2">
         <v>97</v>
@@ -2080,7 +1959,9 @@
       <c r="M5" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="N5" s="2"/>
+      <c r="N5" t="s" s="2">
+        <v>100</v>
+      </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
         <v>73</v>
@@ -2129,7 +2010,7 @@
         <v>73</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>74</v>
@@ -2138,13 +2019,13 @@
         <v>81</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AL5" t="s" s="2">
         <v>73</v>
@@ -2152,21 +2033,21 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>73</v>
@@ -2213,28 +2094,28 @@
         <v>73</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>73</v>
+        <v>109</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="AC6" t="s" s="2">
-        <v>109</v>
+        <v>73</v>
       </c>
       <c r="AD6" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="AF6" t="s" s="2">
         <v>111</v>
@@ -2243,16 +2124,16 @@
         <v>74</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="AL6" t="s" s="2">
         <v>73</v>
@@ -2260,14 +2141,14 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>73</v>
+        <v>113</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2283,19 +2164,19 @@
         <v>73</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2345,7 +2226,7 @@
         <v>73</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>74</v>
@@ -2360,7 +2241,7 @@
         <v>94</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AL7" t="s" s="2">
         <v>73</v>
@@ -2368,21 +2249,21 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>73</v>
+        <v>121</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>73</v>
@@ -2391,19 +2272,19 @@
         <v>73</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2453,22 +2334,22 @@
         <v>73</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="AL8" t="s" s="2">
         <v>73</v>
@@ -2476,10 +2357,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2487,10 +2368,10 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>73</v>
@@ -2499,20 +2380,18 @@
         <v>73</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>128</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>73</v>
@@ -2549,34 +2428,34 @@
         <v>73</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>73</v>
+        <v>131</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>73</v>
+        <v>132</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>73</v>
+        <v>133</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>94</v>
+        <v>135</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="AL9" t="s" s="2">
         <v>73</v>
@@ -2584,12 +2463,14 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="C10" s="2"/>
+        <v>127</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="D10" t="s" s="2">
         <v>73</v>
       </c>
@@ -2598,29 +2479,27 @@
         <v>74</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>134</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="N10" s="2"/>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>73</v>
@@ -2669,7 +2548,7 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
@@ -2681,10 +2560,10 @@
         <v>93</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>94</v>
+        <v>135</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="AL10" t="s" s="2">
         <v>73</v>
@@ -2692,12 +2571,14 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="C11" s="2"/>
+        <v>127</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="D11" t="s" s="2">
         <v>73</v>
       </c>
@@ -2706,29 +2587,27 @@
         <v>74</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="N11" t="s" s="2">
         <v>140</v>
       </c>
+      <c r="N11" s="2"/>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>73</v>
@@ -2753,13 +2632,13 @@
         <v>73</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>141</v>
+        <v>73</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>142</v>
+        <v>73</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>143</v>
+        <v>73</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>73</v>
@@ -2777,7 +2656,7 @@
         <v>73</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>74</v>
@@ -2789,10 +2668,10 @@
         <v>93</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>94</v>
+        <v>135</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>145</v>
+        <v>95</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>73</v>
@@ -2800,43 +2679,43 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="C12" s="2"/>
+        <v>127</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="D12" t="s" s="2">
         <v>73</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>149</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>73</v>
@@ -2861,13 +2740,13 @@
         <v>73</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>150</v>
+        <v>73</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>151</v>
+        <v>73</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>152</v>
+        <v>73</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>73</v>
@@ -2885,7 +2764,7 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
@@ -2897,10 +2776,10 @@
         <v>93</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>94</v>
+        <v>135</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>145</v>
+        <v>95</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>73</v>
@@ -2908,12 +2787,14 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="C13" s="2"/>
+        <v>127</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="D13" t="s" s="2">
         <v>73</v>
       </c>
@@ -2925,26 +2806,24 @@
         <v>81</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>73</v>
@@ -2993,22 +2872,22 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>94</v>
+        <v>135</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>73</v>
@@ -3016,12 +2895,14 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="C14" s="2"/>
+        <v>127</v>
+      </c>
+      <c r="C14" t="s" s="2">
+        <v>151</v>
+      </c>
       <c r="D14" t="s" s="2">
         <v>73</v>
       </c>
@@ -3033,7 +2914,7 @@
         <v>81</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>73</v>
@@ -3042,17 +2923,15 @@
         <v>73</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>73</v>
@@ -3077,13 +2956,13 @@
         <v>73</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>164</v>
+        <v>73</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>165</v>
+        <v>73</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>166</v>
+        <v>73</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>73</v>
@@ -3101,22 +2980,22 @@
         <v>73</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>167</v>
+        <v>134</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>94</v>
+        <v>135</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>73</v>
@@ -3124,14 +3003,16 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="C15" s="2"/>
+        <v>127</v>
+      </c>
+      <c r="C15" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="D15" t="s" s="2">
-        <v>169</v>
+        <v>73</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3141,7 +3022,7 @@
         <v>81</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>73</v>
@@ -3150,17 +3031,15 @@
         <v>73</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>171</v>
+        <v>139</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>173</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>73</v>
@@ -3209,22 +3088,22 @@
         <v>73</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>174</v>
+        <v>134</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>94</v>
+        <v>135</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>175</v>
+        <v>95</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>73</v>
@@ -3232,14 +3111,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3252,24 +3131,26 @@
         <v>73</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="J16" t="s" s="2">
         <v>73</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>178</v>
+        <v>128</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>179</v>
+        <v>158</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>180</v>
+        <v>159</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="O16" s="2"/>
+        <v>160</v>
+      </c>
+      <c r="O16" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="P16" t="s" s="2">
         <v>73</v>
       </c>
@@ -3305,19 +3186,19 @@
         <v>73</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>73</v>
+        <v>131</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>73</v>
+        <v>132</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>73</v>
+        <v>133</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>182</v>
+        <v>162</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>74</v>
@@ -3326,10 +3207,10 @@
         <v>75</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>73</v>
+        <v>135</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>95</v>
@@ -3340,10 +3221,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>183</v>
+        <v>163</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>183</v>
+        <v>163</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3351,30 +3232,32 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>104</v>
+        <v>164</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="N17" s="2"/>
+        <v>166</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>167</v>
+      </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>73</v>
@@ -3411,19 +3294,19 @@
         <v>73</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>109</v>
+        <v>73</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>186</v>
+        <v>163</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>74</v>
@@ -3435,25 +3318,23 @@
         <v>93</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>73</v>
+        <v>168</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>73</v>
+        <v>169</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>187</v>
+        <v>170</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="C18" t="s" s="2">
-        <v>188</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
         <v>73</v>
       </c>
@@ -3465,29 +3346,33 @@
         <v>81</v>
       </c>
       <c r="H18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I18" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="I18" t="s" s="2">
-        <v>73</v>
-      </c>
       <c r="J18" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>190</v>
+        <v>172</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N18" s="2"/>
+        <v>173</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>174</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="Q18" s="2"/>
+      <c r="Q18" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="R18" t="s" s="2">
         <v>73</v>
       </c>
@@ -3531,37 +3416,35 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>95</v>
+        <v>176</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>73</v>
+        <v>177</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="C19" t="s" s="2">
-        <v>193</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
         <v>73</v>
       </c>
@@ -3579,18 +3462,20 @@
         <v>73</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>181</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>73</v>
@@ -3639,22 +3524,22 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>112</v>
+        <v>183</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>95</v>
+        <v>184</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>73</v>
@@ -3662,23 +3547,21 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="C20" t="s" s="2">
-        <v>196</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>73</v>
+        <v>186</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>82</v>
@@ -3687,18 +3570,20 @@
         <v>73</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="N20" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="M20" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>73</v>
@@ -3723,13 +3608,13 @@
         <v>73</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>73</v>
+        <v>191</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>73</v>
+        <v>192</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>73</v>
+        <v>193</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>73</v>
@@ -3747,7 +3632,7 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>74</v>
@@ -3759,54 +3644,54 @@
         <v>93</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>95</v>
+        <v>194</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>73</v>
+        <v>195</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="C21" t="s" s="2">
-        <v>199</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>73</v>
+        <v>197</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J21" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="I21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J21" t="s" s="2">
-        <v>73</v>
-      </c>
       <c r="K21" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="N21" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="L21" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>73</v>
@@ -3831,13 +3716,13 @@
         <v>73</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>73</v>
+        <v>191</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>73</v>
+        <v>201</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>73</v>
+        <v>202</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>73</v>
@@ -3855,7 +3740,7 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>74</v>
@@ -3867,10 +3752,10 @@
         <v>93</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>95</v>
+        <v>203</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>73</v>
@@ -3878,14 +3763,12 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="C22" t="s" s="2">
-        <v>202</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
         <v>73</v>
       </c>
@@ -3894,7 +3777,7 @@
         <v>74</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>82</v>
@@ -3903,18 +3786,20 @@
         <v>73</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>73</v>
@@ -3939,13 +3824,13 @@
         <v>73</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>73</v>
+        <v>208</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>73</v>
+        <v>209</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>73</v>
@@ -3963,7 +3848,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>74</v>
@@ -3975,10 +3860,10 @@
         <v>93</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>95</v>
+        <v>203</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>73</v>
@@ -3986,14 +3871,12 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="C23" t="s" s="2">
-        <v>205</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
         <v>73</v>
       </c>
@@ -4002,27 +3885,29 @@
         <v>74</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J23" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="I23" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J23" t="s" s="2">
-        <v>73</v>
-      </c>
       <c r="K23" t="s" s="2">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>190</v>
+        <v>212</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N23" s="2"/>
+        <v>213</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>73</v>
@@ -4071,7 +3956,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
@@ -4083,57 +3968,55 @@
         <v>93</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>112</v>
+        <v>183</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>95</v>
+        <v>215</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>73</v>
+        <v>216</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J24" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="J24" t="s" s="2">
-        <v>73</v>
-      </c>
       <c r="K24" t="s" s="2">
-        <v>104</v>
+        <v>218</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>210</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>73</v>
       </c>
@@ -4169,34 +4052,34 @@
         <v>73</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>109</v>
+        <v>73</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>95</v>
+        <v>222</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>73</v>
@@ -4204,10 +4087,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4218,7 +4101,7 @@
         <v>74</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>73</v>
@@ -4230,15 +4113,17 @@
         <v>82</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>225</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>73</v>
@@ -4287,13 +4172,13 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>93</v>
@@ -4302,18 +4187,18 @@
         <v>94</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>217</v>
+        <v>73</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4330,30 +4215,28 @@
         <v>73</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="Q26" t="s" s="2">
-        <v>223</v>
-      </c>
+      <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
         <v>73</v>
       </c>
@@ -4397,7 +4280,7 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>74</v>
@@ -4412,18 +4295,18 @@
         <v>94</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>225</v>
+        <v>73</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4446,16 +4329,16 @@
         <v>82</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4505,7 +4388,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>
@@ -4517,10 +4400,10 @@
         <v>93</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>73</v>
@@ -4528,14 +4411,14 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>234</v>
+        <v>73</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4551,19 +4434,19 @@
         <v>73</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4589,31 +4472,31 @@
         <v>73</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>239</v>
+        <v>73</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>240</v>
+        <v>73</v>
       </c>
       <c r="Z28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF28" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="AA28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
@@ -4625,25 +4508,25 @@
         <v>93</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>94</v>
+        <v>246</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>243</v>
+        <v>73</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>245</v>
+        <v>73</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -4659,19 +4542,19 @@
         <v>73</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>235</v>
+        <v>211</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4697,13 +4580,13 @@
         <v>73</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>239</v>
+        <v>73</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>249</v>
+        <v>73</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>250</v>
+        <v>73</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>73</v>
@@ -4721,7 +4604,7 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
@@ -4733,10 +4616,10 @@
         <v>93</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>94</v>
+        <v>183</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>73</v>
@@ -4744,10 +4627,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4761,25 +4644,25 @@
         <v>75</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>235</v>
+        <v>187</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4805,13 +4688,13 @@
         <v>73</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>164</v>
+        <v>257</v>
       </c>
       <c r="Y30" t="s" s="2">
         <v>255</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>73</v>
@@ -4829,7 +4712,7 @@
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
@@ -4844,7 +4727,7 @@
         <v>94</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>73</v>
@@ -4852,10 +4735,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4869,26 +4752,24 @@
         <v>75</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>261</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>73</v>
@@ -4937,7 +4818,7 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
@@ -4949,13 +4830,13 @@
         <v>93</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>231</v>
+        <v>94</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>262</v>
+        <v>102</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>263</v>
+        <v>73</v>
       </c>
     </row>
     <row r="32" hidden="true">
@@ -4977,16 +4858,16 @@
         <v>81</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>97</v>
+        <v>218</v>
       </c>
       <c r="L32" t="s" s="2">
         <v>265</v>
@@ -4994,9 +4875,7 @@
       <c r="M32" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="N32" t="s" s="2">
-        <v>267</v>
-      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>73</v>
@@ -5045,7 +4924,7 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>74</v>
@@ -5054,13 +4933,13 @@
         <v>81</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>268</v>
+        <v>102</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>73</v>
@@ -5068,42 +4947,42 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>73</v>
+        <v>157</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>97</v>
+        <v>128</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="M33" t="s" s="2">
-        <v>271</v>
-      </c>
       <c r="N33" t="s" s="2">
-        <v>272</v>
+        <v>160</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5141,34 +5020,34 @@
         <v>73</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>73</v>
+        <v>131</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>73</v>
+        <v>132</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>73</v>
+        <v>133</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>94</v>
+        <v>135</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>273</v>
+        <v>95</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>73</v>
@@ -5176,44 +5055,46 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>73</v>
+        <v>273</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I34" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="I34" t="s" s="2">
-        <v>73</v>
-      </c>
       <c r="J34" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="L34" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>277</v>
-      </c>
       <c r="N34" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="O34" s="2"/>
+        <v>160</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>73</v>
       </c>
@@ -5261,22 +5142,22 @@
         <v>73</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>94</v>
+        <v>135</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>279</v>
+        <v>95</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>73</v>
@@ -5284,10 +5165,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5301,25 +5182,25 @@
         <v>81</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>281</v>
+        <v>187</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>284</v>
+        <v>200</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5345,10 +5226,10 @@
         <v>73</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>73</v>
+        <v>257</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>73</v>
+        <v>280</v>
       </c>
       <c r="Z35" t="s" s="2">
         <v>73</v>
@@ -5369,7 +5250,7 @@
         <v>73</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>74</v>
@@ -5381,10 +5262,10 @@
         <v>93</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>285</v>
+        <v>94</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>286</v>
+        <v>259</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>73</v>
@@ -5392,10 +5273,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5406,10 +5287,10 @@
         <v>74</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>73</v>
@@ -5418,16 +5299,16 @@
         <v>73</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>288</v>
+        <v>229</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5477,22 +5358,22 @@
         <v>73</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>292</v>
+        <v>94</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>73</v>
@@ -5500,10 +5381,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5517,7 +5398,7 @@
         <v>75</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>73</v>
@@ -5526,16 +5407,16 @@
         <v>73</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>258</v>
+        <v>187</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5561,13 +5442,13 @@
         <v>73</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>73</v>
+        <v>257</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>73</v>
+        <v>290</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>73</v>
+        <v>291</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>73</v>
@@ -5585,7 +5466,7 @@
         <v>73</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>74</v>
@@ -5597,10 +5478,10 @@
         <v>93</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>231</v>
+        <v>94</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>73</v>
@@ -5608,10 +5489,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5634,16 +5515,16 @@
         <v>73</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>235</v>
+        <v>187</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5669,13 +5550,13 @@
         <v>73</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>150</v>
+        <v>191</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>73</v>
@@ -5693,7 +5574,7 @@
         <v>73</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>74</v>
@@ -5708,7 +5589,7 @@
         <v>94</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>73</v>
@@ -5716,10 +5597,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5733,7 +5614,7 @@
         <v>75</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>73</v>
@@ -5742,15 +5623,17 @@
         <v>73</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>306</v>
+        <v>187</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>301</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>302</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>73</v>
@@ -5775,13 +5658,13 @@
         <v>73</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>73</v>
+        <v>109</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>73</v>
@@ -5799,7 +5682,7 @@
         <v>73</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>74</v>
@@ -5814,7 +5697,7 @@
         <v>94</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>101</v>
+        <v>303</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>73</v>
@@ -5822,10 +5705,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5836,7 +5719,7 @@
         <v>74</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>73</v>
@@ -5848,15 +5731,17 @@
         <v>73</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>97</v>
+        <v>187</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>98</v>
+        <v>305</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>306</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>200</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>73</v>
@@ -5881,13 +5766,13 @@
         <v>73</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>73</v>
+        <v>257</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>73</v>
+        <v>307</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>73</v>
+        <v>308</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>73</v>
@@ -5905,22 +5790,22 @@
         <v>73</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>100</v>
+        <v>304</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>101</v>
+        <v>292</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>73</v>
@@ -5928,21 +5813,21 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>73</v>
@@ -5954,17 +5839,15 @@
         <v>73</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>104</v>
+        <v>171</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>105</v>
+        <v>310</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>73</v>
@@ -6001,34 +5884,34 @@
         <v>73</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>109</v>
+        <v>73</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>111</v>
+        <v>309</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>95</v>
+        <v>292</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>73</v>
@@ -6036,14 +5919,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>312</v>
+        <v>73</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6056,13 +5939,13 @@
         <v>73</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>104</v>
+        <v>261</v>
       </c>
       <c r="L42" t="s" s="2">
         <v>313</v>
@@ -6071,11 +5954,9 @@
         <v>314</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>210</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>73</v>
       </c>
@@ -6123,7 +6004,7 @@
         <v>73</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>74</v>
@@ -6135,10 +6016,10 @@
         <v>93</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>95</v>
+        <v>316</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>73</v>
@@ -6146,10 +6027,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6172,17 +6053,15 @@
         <v>73</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>235</v>
+        <v>218</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>317</v>
+        <v>265</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>248</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>73</v>
@@ -6207,10 +6086,10 @@
         <v>73</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>150</v>
+        <v>73</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>319</v>
+        <v>73</v>
       </c>
       <c r="Z43" t="s" s="2">
         <v>73</v>
@@ -6231,7 +6110,7 @@
         <v>73</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>316</v>
+        <v>267</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>74</v>
@@ -6240,13 +6119,13 @@
         <v>81</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>304</v>
+        <v>102</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>73</v>
@@ -6254,21 +6133,21 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>73</v>
+        <v>157</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>73</v>
@@ -6280,16 +6159,16 @@
         <v>73</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>275</v>
+        <v>128</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>321</v>
+        <v>269</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>322</v>
+        <v>270</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>323</v>
+        <v>160</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6327,34 +6206,34 @@
         <v>73</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>73</v>
+        <v>131</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>73</v>
+        <v>132</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>73</v>
+        <v>133</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>320</v>
+        <v>271</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>94</v>
+        <v>135</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>324</v>
+        <v>95</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>73</v>
@@ -6362,14 +6241,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>73</v>
+        <v>273</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6379,27 +6258,29 @@
         <v>75</v>
       </c>
       <c r="H45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I45" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="I45" t="s" s="2">
-        <v>73</v>
-      </c>
       <c r="J45" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>235</v>
+        <v>128</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>326</v>
+        <v>274</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>327</v>
+        <v>275</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="O45" s="2"/>
+        <v>160</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>73</v>
       </c>
@@ -6423,13 +6304,13 @@
         <v>73</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>150</v>
+        <v>73</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>329</v>
+        <v>73</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>330</v>
+        <v>73</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>73</v>
@@ -6447,7 +6328,7 @@
         <v>73</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>325</v>
+        <v>276</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>74</v>
@@ -6459,10 +6340,10 @@
         <v>93</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>94</v>
+        <v>135</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>331</v>
+        <v>95</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>73</v>
@@ -6470,10 +6351,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6496,16 +6377,16 @@
         <v>73</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>235</v>
+        <v>104</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>335</v>
+        <v>221</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6531,13 +6412,13 @@
         <v>73</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>239</v>
+        <v>191</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>336</v>
+        <v>323</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>337</v>
+        <v>324</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>73</v>
@@ -6555,7 +6436,7 @@
         <v>73</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>74</v>
@@ -6570,7 +6451,7 @@
         <v>94</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>331</v>
+        <v>316</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>73</v>
@@ -6578,10 +6459,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>338</v>
+        <v>325</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>338</v>
+        <v>325</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6592,10 +6473,10 @@
         <v>74</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>73</v>
@@ -6604,17 +6485,15 @@
         <v>73</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>235</v>
+        <v>171</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>339</v>
+        <v>326</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>341</v>
-      </c>
+        <v>327</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>73</v>
@@ -6639,13 +6518,13 @@
         <v>73</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>164</v>
+        <v>73</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>165</v>
+        <v>73</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>166</v>
+        <v>73</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>73</v>
@@ -6663,13 +6542,13 @@
         <v>73</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>338</v>
+        <v>325</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>93</v>
@@ -6678,7 +6557,7 @@
         <v>94</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>342</v>
+        <v>316</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>73</v>
@@ -6686,10 +6565,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>343</v>
+        <v>328</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>343</v>
+        <v>328</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6700,10 +6579,10 @@
         <v>74</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>73</v>
@@ -6712,16 +6591,16 @@
         <v>73</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>235</v>
+        <v>329</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>344</v>
+        <v>330</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>345</v>
+        <v>331</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>248</v>
+        <v>332</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6747,13 +6626,13 @@
         <v>73</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>150</v>
+        <v>73</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>346</v>
+        <v>73</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>347</v>
+        <v>73</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>73</v>
@@ -6771,13 +6650,13 @@
         <v>73</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>343</v>
+        <v>328</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>93</v>
@@ -6786,7 +6665,7 @@
         <v>94</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>331</v>
+        <v>316</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>73</v>
@@ -6794,10 +6673,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>348</v>
+        <v>333</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>348</v>
+        <v>333</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6811,7 +6690,7 @@
         <v>81</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>73</v>
@@ -6820,15 +6699,17 @@
         <v>73</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>219</v>
+        <v>329</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>349</v>
+        <v>334</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>335</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>332</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>73</v>
@@ -6877,7 +6758,7 @@
         <v>73</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>348</v>
+        <v>333</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>74</v>
@@ -6892,7 +6773,7 @@
         <v>94</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>331</v>
+        <v>316</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>73</v>
@@ -6900,10 +6781,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>351</v>
+        <v>336</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>351</v>
+        <v>336</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6917,7 +6798,7 @@
         <v>75</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>73</v>
@@ -6926,17 +6807,15 @@
         <v>73</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>306</v>
+        <v>261</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>352</v>
+        <v>337</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>354</v>
-      </c>
+        <v>338</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>73</v>
@@ -6985,7 +6864,7 @@
         <v>73</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>351</v>
+        <v>336</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>74</v>
@@ -7000,7 +6879,7 @@
         <v>94</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>355</v>
+        <v>316</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>73</v>
@@ -7008,10 +6887,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>356</v>
+        <v>339</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>356</v>
+        <v>339</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7034,13 +6913,13 @@
         <v>73</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>97</v>
+        <v>218</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>98</v>
+        <v>265</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>99</v>
+        <v>266</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7091,7 +6970,7 @@
         <v>73</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>100</v>
+        <v>267</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>74</v>
@@ -7106,7 +6985,7 @@
         <v>73</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>73</v>
@@ -7114,14 +6993,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>357</v>
+        <v>340</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>357</v>
+        <v>340</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>103</v>
+        <v>157</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7140,16 +7019,16 @@
         <v>73</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>105</v>
+        <v>269</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>106</v>
+        <v>270</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>107</v>
+        <v>160</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7187,19 +7066,19 @@
         <v>73</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>111</v>
+        <v>271</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>74</v>
@@ -7211,7 +7090,7 @@
         <v>93</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>95</v>
@@ -7222,14 +7101,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>358</v>
+        <v>341</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>358</v>
+        <v>341</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>312</v>
+        <v>273</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -7248,19 +7127,19 @@
         <v>82</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>313</v>
+        <v>274</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>314</v>
+        <v>275</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>107</v>
+        <v>160</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>210</v>
+        <v>161</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>73</v>
@@ -7309,7 +7188,7 @@
         <v>73</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>315</v>
+        <v>276</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>74</v>
@@ -7321,7 +7200,7 @@
         <v>93</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>95</v>
@@ -7332,10 +7211,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>359</v>
+        <v>342</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>359</v>
+        <v>342</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7343,10 +7222,10 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>73</v>
@@ -7358,16 +7237,16 @@
         <v>73</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>160</v>
+        <v>218</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>360</v>
+        <v>343</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>361</v>
+        <v>344</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>267</v>
+        <v>221</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7393,13 +7272,13 @@
         <v>73</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>239</v>
+        <v>73</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>362</v>
+        <v>73</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>363</v>
+        <v>73</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>73</v>
@@ -7417,13 +7296,13 @@
         <v>73</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>359</v>
+        <v>342</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>93</v>
@@ -7432,7 +7311,7 @@
         <v>94</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>355</v>
+        <v>102</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>73</v>
@@ -7440,10 +7319,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>364</v>
+        <v>345</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>364</v>
+        <v>345</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7466,15 +7345,17 @@
         <v>73</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>219</v>
+        <v>346</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>365</v>
+        <v>347</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>348</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>349</v>
+      </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>73</v>
@@ -7523,7 +7404,7 @@
         <v>73</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>364</v>
+        <v>345</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>74</v>
@@ -7535,10 +7416,10 @@
         <v>93</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>94</v>
+        <v>350</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>355</v>
+        <v>316</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>73</v>
@@ -7546,10 +7427,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>367</v>
+        <v>351</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>367</v>
+        <v>351</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7572,16 +7453,16 @@
         <v>73</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>368</v>
+        <v>218</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>369</v>
+        <v>352</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>370</v>
+        <v>353</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>371</v>
+        <v>221</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -7631,7 +7512,7 @@
         <v>73</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>367</v>
+        <v>351</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>74</v>
@@ -7646,7 +7527,7 @@
         <v>94</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>355</v>
+        <v>316</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>73</v>
@@ -7654,10 +7535,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>372</v>
+        <v>354</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>372</v>
+        <v>354</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7668,7 +7549,7 @@
         <v>74</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>73</v>
@@ -7680,16 +7561,16 @@
         <v>73</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>373</v>
+        <v>356</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>374</v>
+        <v>357</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>371</v>
+        <v>214</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -7739,891 +7620,29 @@
         <v>73</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>372</v>
+        <v>354</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>94</v>
+        <v>183</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="58" hidden="true">
-      <c r="A58" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="B58" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="C58" s="2"/>
-      <c r="D58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E58" s="2"/>
-      <c r="F58" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G58" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K58" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
-      <c r="P58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q58" s="2"/>
-      <c r="R58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF58" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="AG58" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH58" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI58" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ58" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK58" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="59" hidden="true">
-      <c r="A59" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="C59" s="2"/>
-      <c r="D59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E59" s="2"/>
-      <c r="F59" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K59" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="L59" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
-      <c r="P59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q59" s="2"/>
-      <c r="R59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AG59" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AK59" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="60" hidden="true">
-      <c r="A60" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="C60" s="2"/>
-      <c r="D60" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="E60" s="2"/>
-      <c r="F60" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G60" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K60" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L60" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="O60" s="2"/>
-      <c r="P60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q60" s="2"/>
-      <c r="R60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="AG60" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH60" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI60" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ60" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="AK60" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="61" hidden="true">
-      <c r="A61" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="C61" s="2"/>
-      <c r="D61" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="E61" s="2"/>
-      <c r="F61" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G61" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K61" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L61" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="P61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q61" s="2"/>
-      <c r="R61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="AG61" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH61" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI61" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ61" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="AK61" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="62" hidden="true">
-      <c r="A62" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="C62" s="2"/>
-      <c r="D62" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E62" s="2"/>
-      <c r="F62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H62" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I62" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J62" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K62" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="L62" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="O62" s="2"/>
-      <c r="P62" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q62" s="2"/>
-      <c r="R62" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S62" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T62" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U62" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V62" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W62" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X62" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y62" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z62" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA62" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="AG62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI62" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ62" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK62" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="63" hidden="true">
-      <c r="A63" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="C63" s="2"/>
-      <c r="D63" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E63" s="2"/>
-      <c r="F63" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H63" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I63" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J63" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K63" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="L63" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="O63" s="2"/>
-      <c r="P63" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q63" s="2"/>
-      <c r="R63" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S63" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T63" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U63" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V63" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W63" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X63" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z63" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="AG63" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI63" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ63" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="AK63" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="64" hidden="true">
-      <c r="A64" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="C64" s="2"/>
-      <c r="D64" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E64" s="2"/>
-      <c r="F64" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I64" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J64" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K64" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="O64" s="2"/>
-      <c r="P64" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q64" s="2"/>
-      <c r="R64" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S64" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T64" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U64" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V64" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W64" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X64" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y64" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z64" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA64" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB64" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD64" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE64" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF64" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="AG64" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI64" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ64" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK64" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="65" hidden="true">
-      <c r="A65" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="C65" s="2"/>
-      <c r="D65" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E65" s="2"/>
-      <c r="F65" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G65" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I65" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J65" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K65" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="L65" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="O65" s="2"/>
-      <c r="P65" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q65" s="2"/>
-      <c r="R65" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S65" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T65" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U65" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V65" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W65" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X65" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z65" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="AG65" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH65" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI65" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ65" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="AK65" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="AL65" t="s" s="2">
         <v>73</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AL65">
+  <autoFilter ref="A1:AL57">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -8633,7 +7652,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI64">
+  <conditionalFormatting sqref="A2:AI56">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T14:04:27+00:00</t>
+    <t>2023-05-02T14:10:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T14:10:11+00:00</t>
+    <t>2023-05-02T14:20:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T14:20:51+00:00</t>
+    <t>2023-05-02T14:32:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T14:32:14+00:00</t>
+    <t>2023-05-02T15:50:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T15:50:41+00:00</t>
+    <t>2023-05-02T16:15:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T16:15:55+00:00</t>
+    <t>2023-05-02T17:25:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T17:25:18+00:00</t>
+    <t>2023-05-02T17:45:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T17:45:11+00:00</t>
+    <t>2023-05-02T17:46:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T17:46:32+00:00</t>
+    <t>2023-05-04T14:01:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T14:01:59+00:00</t>
+    <t>2023-05-04T14:04:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T14:04:48+00:00</t>
+    <t>2023-05-04T14:08:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1972" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1974" uniqueCount="370">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T14:08:50+00:00</t>
+    <t>2023-05-05T17:21:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -440,70 +440,106 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>HealthcareService.extension:activityType</t>
-  </si>
-  <si>
-    <t>activityType</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/HealthcareService-activityType}
+    <t>HealthcareService.extension:as-ext-healthcareservice-activity-type</t>
+  </si>
+  <si>
+    <t>as-ext-healthcareservice-activity-type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire-donnee-publique/StructureDefinition/as-ext-healthcareservice-activity-type}
 </t>
   </si>
   <si>
-    <t>Optional Extensions Element</t>
-  </si>
-  <si>
-    <t>Optional Extension Element - found in all resources.</t>
-  </si>
-  <si>
-    <t>HealthcareService.extension:authorizationDate</t>
-  </si>
-  <si>
-    <t>authorizationDate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/HealthcareService-authorizationDate}
+    <t>activite</t>
+  </si>
+  <si>
+    <t>Code définissant l'activité de soins autorisée -AS- (article L.6122-1 du CSP)</t>
+  </si>
+  <si>
+    <t>la liste des activités de soins soumises à autorisation est fixée par décret en Conseil d'Etat (article L.6122-25 du CSP).</t>
+  </si>
+  <si>
+    <t>HealthcareService.extension:as-ext-healthcareservice-authorization-date</t>
+  </si>
+  <si>
+    <t>as-ext-healthcareservice-authorization-date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire-donnee-publique/StructureDefinition/as-ext-healthcareservice-authorization-date}
 </t>
   </si>
   <si>
-    <t>HealthcareService.extension:authorizationNumberARHGOS</t>
-  </si>
-  <si>
-    <t>authorizationNumberARHGOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/HealthcareService-authorizationNumberARHGOS}
+    <t>Date autorisation</t>
+  </si>
+  <si>
+    <t>Extension créée dans le cadre de l'Annuaire Santé pour prise en compte de la date  délivrance de l’autorisation de l’activité de soins.</t>
+  </si>
+  <si>
+    <t>HealthcareService.extension:as-ext-healthcareservice-authorization-number-arhgos</t>
+  </si>
+  <si>
+    <t>as-ext-healthcareservice-authorization-number-arhgos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire-donnee-publique/StructureDefinition/as-ext-healthcareservice-authorization-number-arhgos}
 </t>
   </si>
   <si>
-    <t>HealthcareService.extension:implementationPeriod</t>
-  </si>
-  <si>
-    <t>implementationPeriod</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/HealthcareService-implementationPeriod}
+    <t>Numéro autorisation ARGHOS</t>
+  </si>
+  <si>
+    <t>Extension créée dans le cadre de l'Annuaire Santé pour prise en compte du numéro d'autorisation ARHGOS.</t>
+  </si>
+  <si>
+    <t>HealthcareService.extension:as-ext-healthcareservice-implementation-period</t>
+  </si>
+  <si>
+    <t>as-ext-healthcareservice-implementation-period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire-donnee-publique/StructureDefinition/as-ext-healthcareservice-implementation-period}
 </t>
   </si>
   <si>
-    <t>HealthcareService.extension:deleteAutorisationImplantation</t>
-  </si>
-  <si>
-    <t>deleteAutorisationImplantation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/HealthcareService-deleteAutorisationImplantation}
+    <t>AS HealthcareService Implementation Period Extension</t>
+  </si>
+  <si>
+    <t>Extension créée dans le cadre de l'Annuaire Santé pour en compte de la date d'échéance de l'autorisation de l'activité de soins.</t>
+  </si>
+  <si>
+    <t>HealthcareService.extension:as-ext-healthcareservice-delete-autorization-implantation</t>
+  </si>
+  <si>
+    <t>as-ext-healthcareservice-delete-autorization-implantation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire-donnee-publique/StructureDefinition/as-ext-healthcareservice-delete-autorization-implantation}
 </t>
   </si>
   <si>
-    <t>HealthcareService.extension:dateUpdateActivity</t>
-  </si>
-  <si>
-    <t>dateUpdateActivity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/HealthcareService-dateUpdateActivity}
+    <t>suppressionAutorisation</t>
+  </si>
+  <si>
+    <t>ndicateur de suppression de l'autorisation de l'activité de soins.</t>
+  </si>
+  <si>
+    <t>Donnée propre à FINESS</t>
+  </si>
+  <si>
+    <t>HealthcareService.extension:as-ext-healthcareservice-date-update-activity</t>
+  </si>
+  <si>
+    <t>as-ext-healthcareservice-date-update-activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire-donnee-publique/StructureDefinition/as-ext-healthcareservice-date-update-activity}
 </t>
+  </si>
+  <si>
+    <t>dateMajAutorisation</t>
+  </si>
+  <si>
+    <t>Date de dernière mise à jour de l’autorisation.</t>
   </si>
   <si>
     <t>HealthcareService.modifierExtension</t>
@@ -536,7 +572,7 @@
 </t>
   </si>
   <si>
-    <t>numeroAutorisationARHGOS</t>
+    <t>"numeroAutorisationARHGOS"as-ext-healthcareservice-date-update-activity</t>
   </si>
   <si>
     <t>External identifiers for this item.</t>
@@ -660,9 +696,6 @@
   </si>
   <si>
     <t>HealthcareService.specialty</t>
-  </si>
-  <si>
-    <t>activite</t>
   </si>
   <si>
     <t>Collection of specialties handled by the service site. This is more of a medical term.</t>
@@ -1448,9 +1481,9 @@
   <dimension ref="A1:AL57"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="56.546875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="81.09375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="49.1328125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="29.5703125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="54.1171875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -2499,7 +2532,9 @@
       <c r="M10" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="N10" s="2"/>
+      <c r="N10" t="s" s="2">
+        <v>141</v>
+      </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>73</v>
@@ -2563,7 +2598,7 @@
         <v>135</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="AL10" t="s" s="2">
         <v>73</v>
@@ -2571,13 +2606,13 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B11" t="s" s="2">
         <v>127</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>73</v>
@@ -2599,13 +2634,13 @@
         <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2671,7 +2706,7 @@
         <v>135</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>73</v>
@@ -2679,13 +2714,13 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>127</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>73</v>
@@ -2707,13 +2742,13 @@
         <v>73</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2779,7 +2814,7 @@
         <v>135</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>73</v>
@@ -2787,13 +2822,13 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="B13" t="s" s="2">
         <v>127</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="D13" t="s" s="2">
         <v>73</v>
@@ -2815,13 +2850,13 @@
         <v>73</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2887,7 +2922,7 @@
         <v>135</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>73</v>
@@ -2895,13 +2930,13 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="B14" t="s" s="2">
         <v>127</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="D14" t="s" s="2">
         <v>73</v>
@@ -2923,15 +2958,17 @@
         <v>73</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="N14" s="2"/>
+        <v>161</v>
+      </c>
+      <c r="N14" t="s" s="2">
+        <v>162</v>
+      </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>73</v>
@@ -2995,7 +3032,7 @@
         <v>135</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>73</v>
@@ -3003,13 +3040,13 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="B15" t="s" s="2">
         <v>127</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>73</v>
@@ -3031,13 +3068,13 @@
         <v>73</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>139</v>
+        <v>166</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>140</v>
+        <v>167</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3103,7 +3140,7 @@
         <v>135</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>73</v>
@@ -3111,14 +3148,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3140,16 +3177,16 @@
         <v>128</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>73</v>
@@ -3198,7 +3235,7 @@
         <v>133</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>74</v>
@@ -3221,10 +3258,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3247,16 +3284,16 @@
         <v>82</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3306,7 +3343,7 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>74</v>
@@ -3321,18 +3358,18 @@
         <v>94</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>169</v>
+        <v>181</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3355,23 +3392,23 @@
         <v>82</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>73</v>
       </c>
       <c r="Q18" t="s" s="2">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="R18" t="s" s="2">
         <v>73</v>
@@ -3416,7 +3453,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
@@ -3431,18 +3468,18 @@
         <v>94</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>177</v>
+        <v>189</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3465,16 +3502,16 @@
         <v>82</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3524,7 +3561,7 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
@@ -3536,10 +3573,10 @@
         <v>93</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>73</v>
@@ -3547,14 +3584,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3573,16 +3610,16 @@
         <v>82</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3608,13 +3645,13 @@
         <v>73</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>73</v>
@@ -3632,7 +3669,7 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>74</v>
@@ -3647,22 +3684,22 @@
         <v>94</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>195</v>
+        <v>207</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -3681,16 +3718,16 @@
         <v>82</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3716,13 +3753,13 @@
         <v>73</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>73</v>
@@ -3740,7 +3777,7 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>74</v>
@@ -3755,7 +3792,7 @@
         <v>94</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>73</v>
@@ -3763,10 +3800,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3789,16 +3826,16 @@
         <v>82</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>205</v>
+        <v>139</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3827,10 +3864,10 @@
         <v>108</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>73</v>
@@ -3848,7 +3885,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>74</v>
@@ -3863,7 +3900,7 @@
         <v>94</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>73</v>
@@ -3871,10 +3908,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3897,16 +3934,16 @@
         <v>82</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -3956,7 +3993,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
@@ -3968,21 +4005,21 @@
         <v>93</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>216</v>
+        <v>227</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4005,16 +4042,16 @@
         <v>82</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4064,7 +4101,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
@@ -4079,7 +4116,7 @@
         <v>94</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>73</v>
@@ -4087,10 +4124,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4113,16 +4150,16 @@
         <v>82</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4172,7 +4209,7 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
@@ -4187,7 +4224,7 @@
         <v>94</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>73</v>
@@ -4195,10 +4232,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4221,16 +4258,16 @@
         <v>73</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4280,7 +4317,7 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>74</v>
@@ -4295,7 +4332,7 @@
         <v>94</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>73</v>
@@ -4303,10 +4340,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4329,16 +4366,16 @@
         <v>82</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4388,7 +4425,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>
@@ -4400,10 +4437,10 @@
         <v>93</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>73</v>
@@ -4411,10 +4448,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4437,16 +4474,16 @@
         <v>73</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4496,7 +4533,7 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
@@ -4508,10 +4545,10 @@
         <v>93</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>73</v>
@@ -4519,10 +4556,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4545,16 +4582,16 @@
         <v>73</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4604,7 +4641,7 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
@@ -4616,10 +4653,10 @@
         <v>93</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>73</v>
@@ -4627,10 +4664,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4653,16 +4690,16 @@
         <v>73</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4688,13 +4725,13 @@
         <v>73</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>73</v>
@@ -4712,7 +4749,7 @@
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
@@ -4727,7 +4764,7 @@
         <v>94</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>73</v>
@@ -4735,10 +4772,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4761,13 +4798,13 @@
         <v>73</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4818,7 +4855,7 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
@@ -4841,10 +4878,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4867,13 +4904,13 @@
         <v>73</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4924,7 +4961,7 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>74</v>
@@ -4947,14 +4984,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -4976,13 +5013,13 @@
         <v>128</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5032,7 +5069,7 @@
         <v>133</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>74</v>
@@ -5055,14 +5092,14 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5084,16 +5121,16 @@
         <v>128</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>73</v>
@@ -5142,7 +5179,7 @@
         <v>73</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>74</v>
@@ -5165,10 +5202,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5191,16 +5228,16 @@
         <v>73</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5226,10 +5263,10 @@
         <v>73</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="Z35" t="s" s="2">
         <v>73</v>
@@ -5250,7 +5287,7 @@
         <v>73</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>74</v>
@@ -5265,7 +5302,7 @@
         <v>94</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>73</v>
@@ -5273,10 +5310,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5299,16 +5336,16 @@
         <v>73</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5358,7 +5395,7 @@
         <v>73</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>74</v>
@@ -5373,7 +5410,7 @@
         <v>94</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>73</v>
@@ -5381,10 +5418,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5407,16 +5444,16 @@
         <v>73</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5442,13 +5479,13 @@
         <v>73</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>73</v>
@@ -5466,7 +5503,7 @@
         <v>73</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>74</v>
@@ -5481,7 +5518,7 @@
         <v>94</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>73</v>
@@ -5489,10 +5526,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5515,16 +5552,16 @@
         <v>73</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5550,13 +5587,13 @@
         <v>73</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>297</v>
+        <v>308</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>73</v>
@@ -5574,7 +5611,7 @@
         <v>73</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>74</v>
@@ -5589,7 +5626,7 @@
         <v>94</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>73</v>
@@ -5597,10 +5634,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5623,16 +5660,16 @@
         <v>73</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>302</v>
+        <v>313</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -5682,7 +5719,7 @@
         <v>73</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>74</v>
@@ -5697,7 +5734,7 @@
         <v>94</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>73</v>
@@ -5705,10 +5742,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5731,16 +5768,16 @@
         <v>73</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -5766,13 +5803,13 @@
         <v>73</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>73</v>
@@ -5790,7 +5827,7 @@
         <v>73</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>74</v>
@@ -5805,7 +5842,7 @@
         <v>94</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>73</v>
@@ -5813,10 +5850,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5839,13 +5876,13 @@
         <v>73</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5896,7 +5933,7 @@
         <v>73</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>74</v>
@@ -5911,7 +5948,7 @@
         <v>94</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>73</v>
@@ -5919,10 +5956,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5945,16 +5982,16 @@
         <v>73</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6004,7 +6041,7 @@
         <v>73</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>74</v>
@@ -6019,7 +6056,7 @@
         <v>94</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>73</v>
@@ -6027,10 +6064,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6053,13 +6090,13 @@
         <v>73</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6110,7 +6147,7 @@
         <v>73</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>74</v>
@@ -6133,14 +6170,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6162,13 +6199,13 @@
         <v>128</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6218,7 +6255,7 @@
         <v>133</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>74</v>
@@ -6241,14 +6278,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6270,16 +6307,16 @@
         <v>128</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>73</v>
@@ -6328,7 +6365,7 @@
         <v>73</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>74</v>
@@ -6351,10 +6388,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6380,13 +6417,13 @@
         <v>104</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6412,13 +6449,13 @@
         <v>73</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>73</v>
@@ -6436,7 +6473,7 @@
         <v>73</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>74</v>
@@ -6451,7 +6488,7 @@
         <v>94</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>73</v>
@@ -6459,10 +6496,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6485,13 +6522,13 @@
         <v>73</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>327</v>
+        <v>338</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6542,7 +6579,7 @@
         <v>73</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>74</v>
@@ -6557,7 +6594,7 @@
         <v>94</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>73</v>
@@ -6565,10 +6602,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6591,16 +6628,16 @@
         <v>73</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6650,7 +6687,7 @@
         <v>73</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>74</v>
@@ -6665,7 +6702,7 @@
         <v>94</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>73</v>
@@ -6673,10 +6710,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6699,16 +6736,16 @@
         <v>73</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>335</v>
+        <v>346</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -6758,7 +6795,7 @@
         <v>73</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>74</v>
@@ -6773,7 +6810,7 @@
         <v>94</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>73</v>
@@ -6781,10 +6818,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6807,13 +6844,13 @@
         <v>73</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>338</v>
+        <v>349</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6864,7 +6901,7 @@
         <v>73</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>74</v>
@@ -6879,7 +6916,7 @@
         <v>94</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>73</v>
@@ -6887,10 +6924,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6913,13 +6950,13 @@
         <v>73</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6970,7 +7007,7 @@
         <v>73</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>74</v>
@@ -6993,14 +7030,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7022,13 +7059,13 @@
         <v>128</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7078,7 +7115,7 @@
         <v>133</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>74</v>
@@ -7101,14 +7138,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -7130,16 +7167,16 @@
         <v>128</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>73</v>
@@ -7188,7 +7225,7 @@
         <v>73</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>74</v>
@@ -7211,10 +7248,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7237,16 +7274,16 @@
         <v>73</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>343</v>
+        <v>354</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7296,7 +7333,7 @@
         <v>73</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -7319,10 +7356,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>345</v>
+        <v>356</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>345</v>
+        <v>356</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7345,16 +7382,16 @@
         <v>73</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>349</v>
+        <v>360</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7404,7 +7441,7 @@
         <v>73</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>345</v>
+        <v>356</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>74</v>
@@ -7416,10 +7453,10 @@
         <v>93</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>73</v>
@@ -7427,10 +7464,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7453,16 +7490,16 @@
         <v>73</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -7512,7 +7549,7 @@
         <v>73</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>74</v>
@@ -7527,7 +7564,7 @@
         <v>94</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>73</v>
@@ -7535,10 +7572,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7561,16 +7598,16 @@
         <v>73</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -7620,7 +7657,7 @@
         <v>73</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>74</v>
@@ -7632,10 +7669,10 @@
         <v>93</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>73</v>
